--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z27" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.75</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>5.7</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z29" t="n">
         <v>1.75</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
         <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AA30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="M32" t="n">
         <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="M35" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.15</v>
+        <v>1.88</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5079,37 +5079,37 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,22 +5184,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.88</v>
+        <v>4.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="O37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -5208,37 +5208,37 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>5.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="M40" t="n">
         <v>4.15</v>
       </c>
       <c r="N40" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="M41" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z41" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>5.1</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="M43" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="N43" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.19</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>1.19</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>14</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.1</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2</v>
-      </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z34" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M35" t="n">
         <v>3.45</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.8</v>
-      </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.88</v>
+        <v>4.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="N36" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="O36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5079,37 +5079,37 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="M37" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N37" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="N38" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="M40" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="N40" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,22 +5700,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="M41" t="n">
         <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5724,37 +5724,37 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="N43" t="n">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK44"/>
+  <dimension ref="A1:AK43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>4.21</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45951.54166666666</v>
+        <v>45951.57291666666</v>
       </c>
     </row>
     <row r="9">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45951.57291666666</v>
+        <v>45951.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45951.58333333334</v>
+        <v>45951.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45951.60416666666</v>
+        <v>45951.625</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45951.625</v>
+        <v>45951.65625</v>
       </c>
     </row>
     <row r="25">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N26" t="n">
-        <v>2.18</v>
+        <v>5.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
         <v>2.4</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="O29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45951.65625</v>
+        <v>45951.66666666666</v>
       </c>
     </row>
     <row r="35">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="M36" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="N36" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="M37" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.55</v>
+        <v>4.3</v>
       </c>
       <c r="M40" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="N40" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,22 +5700,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5724,37 +5724,37 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,22 +5829,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.45</v>
+        <v>1.88</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5853,37 +5853,37 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,22 +5958,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="M43" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>4.4</v>
+        <v>2.26</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6031,141 +6031,12 @@
         <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45951.66666666666</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>45951</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Luxembourg National Division</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Swift Hesperange</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Racing</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="O44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK44" s="3" t="n">
         <v>45951.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>1.19</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.19</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z25" t="n">
         <v>2.1</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2</v>
-      </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="M34" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="N34" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="M35" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="N35" t="n">
         <v>1.7</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="M36" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="M40" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.19</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>14</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,62 +3636,62 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD25" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
         <v>2.4</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Z30" t="n">
         <v>1.75</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z31" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z32" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.75</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="M34" t="n">
         <v>4.15</v>
       </c>
       <c r="N34" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="M35" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="N35" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z36" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="M37" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>5.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.1</v>
+        <v>1.55</v>
       </c>
       <c r="M39" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="N39" t="n">
-        <v>1.6</v>
+        <v>6.1</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.55</v>
+        <v>4.3</v>
       </c>
       <c r="M41" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="N41" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK43"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>5.55</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>2.35</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N8" t="n">
         <v>2.55</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
         <v>1.77</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45951.60416666666</v>
+        <v>45951.625</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
         <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>2.18</v>
+        <v>5.7</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>5.7</v>
+        <v>2.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="M34" t="n">
-        <v>4.15</v>
+        <v>3.99</v>
       </c>
       <c r="N34" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.7</v>
+        <v>3.62</v>
       </c>
       <c r="M35" t="n">
-        <v>4.15</v>
+        <v>3.52</v>
       </c>
       <c r="N35" t="n">
-        <v>4.4</v>
+        <v>1.96</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.6</v>
+        <v>4.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="M38" t="n">
         <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.55</v>
+        <v>2.99</v>
       </c>
       <c r="M39" t="n">
-        <v>4.05</v>
+        <v>3.64</v>
       </c>
       <c r="N39" t="n">
-        <v>6.1</v>
+        <v>2.17</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.3</v>
+        <v>1.57</v>
       </c>
       <c r="M41" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="N41" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,22 +5829,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.88</v>
+        <v>2.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>2.26</v>
       </c>
       <c r="O42" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="P42" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5853,37 +5853,37 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,147 +5896,18 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45951.66666666666</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>45951</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Luxembourg National Division</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Swift Hesperange</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Racing</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK43" s="3" t="n">
         <v>45951.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45951.57291666666</v>
+        <v>45951.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45951.57291666666</v>
+        <v>45951.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45951.58333333334</v>
+        <v>45951.57291666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45951.60416666666</v>
+        <v>45951.57291666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45951.60416666666</v>
+        <v>45951.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45951.625</v>
+        <v>45951.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45951.625</v>
+        <v>45951.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45951.65625</v>
+        <v>45951.625</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45951.65625</v>
+        <v>45951.625</v>
       </c>
     </row>
     <row r="26">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,62 +4152,62 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA29" t="n">
         <v>3</v>
       </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="AB29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45951.66666666666</v>
+        <v>45951.65625</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.62</v>
+        <v>2.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45951.66666666666</v>
+        <v>45951.65625</v>
       </c>
     </row>
     <row r="36">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="N36" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>4.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>3.99</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.99</v>
+        <v>1.62</v>
       </c>
       <c r="M39" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.17</v>
+        <v>4.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.57</v>
+        <v>4.1</v>
       </c>
       <c r="M41" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>5.5</v>
+        <v>1.73</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,22 +5829,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.8</v>
+        <v>3.62</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="N42" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="O42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5871,43 +5871,301 @@
         <v>1.8</v>
       </c>
       <c r="Z42" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
+        <v>45951.66666666666</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="n">
+        <v>45951.66666666666</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Luxembourg National Division</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Swift Hesperange</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z44" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
         <v>2.1</v>
       </c>
-      <c r="AJ42" t="n">
+      <c r="AJ44" t="n">
         <v>1.8</v>
       </c>
-      <c r="AK42" s="3" t="n">
+      <c r="AK44" s="3" t="n">
         <v>45951.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M10" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
         <v>2.4</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.04</v>
+        <v>3.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>5.7</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,62 +4539,62 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA32" t="n">
         <v>3</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
+      <c r="AB32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD32" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.8</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.99</v>
+        <v>4.8</v>
       </c>
       <c r="M43" t="n">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.17</v>
+        <v>1.61</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M11" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>5.7</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
         <v>2.4</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M31" t="n">
         <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.04</v>
+        <v>3.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.75</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.5</v>
+        <v>1.62</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="M37" t="n">
-        <v>3.99</v>
+        <v>3.52</v>
       </c>
       <c r="N37" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.99</v>
+        <v>4.8</v>
       </c>
       <c r="M40" t="n">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>2.17</v>
+        <v>1.61</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.52</v>
+        <v>3.99</v>
       </c>
       <c r="N42" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.8</v>
+        <v>1.57</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="N43" t="n">
-        <v>1.61</v>
+        <v>5.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK44"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45951.41666666666</v>
+        <v>45951.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45951.45833333334</v>
+        <v>45951.47916666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45951.47916666666</v>
+        <v>45951.5</v>
       </c>
     </row>
     <row r="6">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45951.5</v>
+        <v>45951.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45951.54166666666</v>
+        <v>45951.57291666666</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M10" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45951.57291666666</v>
+        <v>45951.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45951.625</v>
+        <v>45951.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,14 +3765,14 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N26" t="n">
         <v>2.4</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3</v>
-      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,62 +3894,62 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA27" t="n">
         <v>3</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
+      <c r="AB27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD27" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
       <c r="AE27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
         <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z33" t="n">
         <v>1.75</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.52</v>
+        <v>3.99</v>
       </c>
       <c r="N37" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.99</v>
+        <v>3.62</v>
       </c>
       <c r="M38" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="N38" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.8</v>
+        <v>1.62</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>1.61</v>
+        <v>4.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.1</v>
+        <v>1.57</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="N41" t="n">
-        <v>1.73</v>
+        <v>5.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5825,65 +5825,65 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.3</v>
+        <v>1.93</v>
       </c>
       <c r="M42" t="n">
-        <v>3.99</v>
+        <v>3.75</v>
       </c>
       <c r="N42" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.57</v>
+        <v>4.8</v>
       </c>
       <c r="M43" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>5.5</v>
+        <v>1.61</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6046,126 +6046,255 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3" t="n">
+        <v>45951.66666666666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Luxembourg National Division</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Swift Hesperange</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Racing</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="L45" t="n">
         <v>2.8</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M45" t="n">
         <v>3.4</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N45" t="n">
         <v>2.26</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O45" t="n">
         <v>3.25</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P45" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q45" t="n">
         <v>2.62</v>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="Z45" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
         <v>2.1</v>
       </c>
-      <c r="AJ44" t="n">
+      <c r="AJ45" t="n">
         <v>1.8</v>
       </c>
-      <c r="AK44" s="3" t="n">
+      <c r="AK45" s="3" t="n">
         <v>45951.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M9" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>5.7</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
         <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.75</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="N36" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z36" t="n">
         <v>1.85</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.95</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.3</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.62</v>
+        <v>4.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.62</v>
+        <v>2.99</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N40" t="n">
-        <v>4.75</v>
+        <v>2.17</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.57</v>
+        <v>3.62</v>
       </c>
       <c r="M41" t="n">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
       <c r="N41" t="n">
-        <v>5.5</v>
+        <v>1.96</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5825,65 +5825,65 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.93</v>
+        <v>4.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.75</v>
+        <v>3.99</v>
       </c>
       <c r="N42" t="n">
-        <v>3.5</v>
+        <v>1.71</v>
       </c>
       <c r="O42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.8</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>1.61</v>
+        <v>4.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,22 +6087,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6160,141 +6160,12 @@
         <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45951.66666666666</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>45951</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Luxembourg National Division</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Swift Hesperange</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Racing</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N45" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="O45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK45" s="3" t="n">
         <v>45951.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N2" t="n">
         <v>12</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M10" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3768,7 +3768,7 @@
         <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
         <v>3</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M29" t="n">
         <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.05</v>
+        <v>2.03</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>3.06</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>5.7</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,14 +4926,14 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N35" t="n">
         <v>2.4</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3</v>
-      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>3.62</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.8</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N39" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.99</v>
+        <v>1.57</v>
       </c>
       <c r="M40" t="n">
-        <v>3.64</v>
+        <v>3.98</v>
       </c>
       <c r="N40" t="n">
-        <v>2.17</v>
+        <v>5.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.52</v>
+        <v>3.99</v>
       </c>
       <c r="N41" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="M42" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,55 +5958,55 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.62</v>
-      </c>
-      <c r="M43" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA27" t="n">
         <v>3</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>3.06</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="Z33" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>4.3</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="N36" t="n">
-        <v>4.75</v>
+        <v>1.71</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.62</v>
+        <v>4.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="N37" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.3</v>
+        <v>1.62</v>
       </c>
       <c r="M41" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>1.71</v>
+        <v>4.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="N42" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.8</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M9" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.8</v>
+        <v>2.03</v>
       </c>
       <c r="M28" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3.6</v>
       </c>
-      <c r="N28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y28" t="n">
         <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Z29" t="n">
         <v>1.75</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,14 +4281,14 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N30" t="n">
         <v>2.4</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3</v>
-      </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z31" t="n">
         <v>1.75</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M33" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="M36" t="n">
-        <v>3.99</v>
+        <v>3.64</v>
       </c>
       <c r="N36" t="n">
-        <v>1.71</v>
+        <v>2.17</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.8</v>
+        <v>1.57</v>
       </c>
       <c r="M37" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="N37" t="n">
-        <v>1.61</v>
+        <v>5.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.99</v>
+        <v>4.1</v>
       </c>
       <c r="M39" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.52</v>
+        <v>3.99</v>
       </c>
       <c r="N42" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>3.62</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,17 +2213,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,14 +3894,14 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N27" t="n">
         <v>2.4</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3</v>
-      </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.03</v>
+        <v>3.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>3.06</v>
+        <v>1.97</v>
       </c>
       <c r="O28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,14 +4410,14 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N31" t="n">
         <v>2.4</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3</v>
-      </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,49 +4797,49 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M34" t="n">
         <v>3.4</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.75</v>
-      </c>
       <c r="N34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>2.05</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.75</v>
-      </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>3.99</v>
       </c>
       <c r="N38" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>4.8</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.3</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK44"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>2.13</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.15</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>3.06</v>
+        <v>2.05</v>
       </c>
       <c r="O26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,62 +4539,62 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.4</v>
+        <v>2.03</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="N32" t="n">
-        <v>2.05</v>
+        <v>3.06</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD32" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,14 +4668,14 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N33" t="n">
         <v>2.4</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3</v>
-      </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.99</v>
+        <v>4.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="N36" t="n">
-        <v>2.17</v>
+        <v>1.61</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.57</v>
+        <v>4.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="N37" t="n">
-        <v>5.5</v>
+        <v>1.71</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.3</v>
+        <v>1.62</v>
       </c>
       <c r="M38" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>1.71</v>
+        <v>4.75</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.8</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.62</v>
+        <v>2.99</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N41" t="n">
-        <v>4.75</v>
+        <v>2.17</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>3.62</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.62</v>
+        <v>1.92</v>
       </c>
       <c r="M43" t="n">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.96</v>
+        <v>3.5</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6046,126 +6046,255 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3" t="n">
+        <v>45951.66666666666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Luxembourg National Division</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Swift Hesperange</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Racing</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="L45" t="n">
         <v>2.8</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M45" t="n">
         <v>3.4</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N45" t="n">
         <v>2.26</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O45" t="n">
         <v>3.25</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P45" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q45" t="n">
         <v>2.62</v>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="Z45" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
         <v>2.1</v>
       </c>
-      <c r="AJ44" t="n">
+      <c r="AJ45" t="n">
         <v>1.8</v>
       </c>
-      <c r="AK44" s="3" t="n">
+      <c r="AK45" s="3" t="n">
         <v>45951.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>4.22</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N6" t="n">
-        <v>4.22</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.75</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA29" t="n">
         <v>3</v>
       </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="M31" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.03</v>
+        <v>3.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.06</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.8</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.3</v>
+        <v>1.62</v>
       </c>
       <c r="M37" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>1.71</v>
+        <v>4.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>2.99</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N38" t="n">
-        <v>4.75</v>
+        <v>2.17</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="N39" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z40" t="n">
         <v>1.85</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.95</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.99</v>
+        <v>3.62</v>
       </c>
       <c r="M41" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="N41" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="M42" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.57</v>
+        <v>4.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="N44" t="n">
-        <v>5.5</v>
+        <v>1.61</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -672,58 +672,58 @@
         <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -927,55 +927,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC4" t="n">
         <v>2</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M10" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.04</v>
+        <v>3.15</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>2.22</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.1</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N18" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,14 +3765,14 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N26" t="n">
         <v>2.4</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3</v>
-      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AA29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.55</v>
+        <v>2.03</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="N33" t="n">
-        <v>1.97</v>
+        <v>3.06</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.62</v>
+        <v>3.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>5.7</v>
+        <v>1.97</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>4.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.99</v>
       </c>
       <c r="N36" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.3</v>
+        <v>1.92</v>
       </c>
       <c r="M39" t="n">
-        <v>3.99</v>
+        <v>3.65</v>
       </c>
       <c r="N39" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.62</v>
+        <v>4.8</v>
       </c>
       <c r="M41" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="N41" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.1</v>
+        <v>1.62</v>
       </c>
       <c r="M42" t="n">
         <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>1.73</v>
+        <v>4.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.92</v>
+        <v>3.62</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="N43" t="n">
-        <v>3.5</v>
+        <v>1.96</v>
       </c>
       <c r="O43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="M44" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.22</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>4.22</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M9" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>3.78</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.15</v>
+        <v>2.04</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>2.22</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,62 +4023,62 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.4</v>
+        <v>2.03</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>3.06</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD28" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N32" t="n">
-        <v>5.7</v>
+        <v>2.05</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.3</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>4.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.99</v>
+        <v>1.62</v>
       </c>
       <c r="M38" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.17</v>
+        <v>4.75</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="M39" t="n">
-        <v>3.65</v>
+        <v>3.98</v>
       </c>
       <c r="N39" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="O39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>4.1</v>
       </c>
       <c r="M40" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>5.5</v>
+        <v>1.73</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="M41" t="n">
-        <v>4.2</v>
+        <v>3.99</v>
       </c>
       <c r="N41" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.62</v>
+        <v>3.62</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="N42" t="n">
-        <v>4.75</v>
+        <v>1.96</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.62</v>
+        <v>1.92</v>
       </c>
       <c r="M43" t="n">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.96</v>
+        <v>3.5</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N44" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,10 +672,10 @@
         <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="N2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>1.78</v>
@@ -696,7 +696,7 @@
         <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
@@ -708,10 +708,10 @@
         <v>3.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
         <v>3.2</v>
@@ -723,7 +723,7 @@
         <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>2.3</v>
@@ -966,10 +966,10 @@
         <v>2.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
         <v>3.72</v>
@@ -978,7 +978,7 @@
         <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD4" t="n">
         <v>1.72</v>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
         <v>1.87</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>4.22</v>
       </c>
       <c r="O5" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>4.9</v>
+        <v>4.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N6" t="n">
-        <v>4.22</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="T6" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="U6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.56</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AC6" t="n">
         <v>1.54</v>
       </c>
-      <c r="Z6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AD6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1323,13 +1323,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1338,37 +1338,37 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X14" t="n">
         <v>3.1</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,65 +2342,65 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.04</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="Q17" t="n">
         <v>3.25</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.98</v>
+        <v>3.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45951.60416666666</v>
+        <v>45951.625</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.62</v>
+        <v>3.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.85</v>
+        <v>3.06</v>
       </c>
       <c r="N26" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
         <v>2.4</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.22</v>
       </c>
-      <c r="X28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.55</v>
+        <v>2.37</v>
       </c>
       <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3.45</v>
       </c>
-      <c r="N30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y32" t="n">
         <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.5</v>
+        <v>3.46</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="Z34" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="N36" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.8</v>
+        <v>1.57</v>
       </c>
       <c r="M37" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="N37" t="n">
-        <v>1.61</v>
+        <v>5.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.57</v>
+        <v>4.8</v>
       </c>
       <c r="M39" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="N39" t="n">
-        <v>5.5</v>
+        <v>1.61</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.62</v>
+        <v>1.62</v>
       </c>
       <c r="M42" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>1.96</v>
+        <v>4.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.92</v>
+        <v>3.62</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="N43" t="n">
-        <v>3.5</v>
+        <v>1.96</v>
       </c>
       <c r="O43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="M44" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>2.17</v>
+        <v>3.6</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6167,135 +6167,6 @@
       </c>
       <c r="AK44" s="3" t="n">
         <v>45951.66666666666</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>45951</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Luxembourg National Division</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Swift Hesperange</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Racing</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N45" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="O45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK45" s="3" t="n">
-        <v>45951.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -678,10 +678,10 @@
         <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="P2" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
         <v>8.5</v>
@@ -690,7 +690,7 @@
         <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>2.7</v>
@@ -705,7 +705,7 @@
         <v>1.26</v>
       </c>
       <c r="X2" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="Y2" t="n">
         <v>1.9</v>
@@ -723,7 +723,7 @@
         <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>3.14</v>
+        <v>5.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.78</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>4.35</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M10" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.56</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.93</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>4.25</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>5.9</v>
+        <v>3.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>3.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,34 +2217,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.25</v>
+        <v>4.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
         <v>1.02</v>
@@ -2253,25 +2253,25 @@
         <v>1.28</v>
       </c>
       <c r="X14" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.46</v>
+        <v>1.95</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB14" t="n">
         <v>1.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>4.32</v>
+        <v>3.45</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.41</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,77 +2475,77 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.69</v>
+        <v>4.32</v>
       </c>
       <c r="P16" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.65</v>
+        <v>2.79</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.28</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
         <v>4.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="T18" t="n">
-        <v>3.26</v>
+        <v>2.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="X18" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.25</v>
+        <v>3.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>3.38</v>
+        <v>3.06</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.4</v>
+        <v>3.99</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.16</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q20" t="n">
-        <v>2.7</v>
+        <v>4.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X20" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>3.02</v>
@@ -3528,7 +3528,7 @@
         <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="T24" t="n">
         <v>2.96</v>
@@ -3546,10 +3546,10 @@
         <v>2.88</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AA24" t="n">
         <v>3.5</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,77 +3765,77 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="M26" t="n">
-        <v>3.06</v>
+        <v>3.64</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X26" t="n">
         <v>4</v>
       </c>
-      <c r="P26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="Y26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.26</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.77</v>
+        <v>1.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>6.51</v>
       </c>
       <c r="O27" t="n">
-        <v>3.46</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.97</v>
+        <v>5.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="T27" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>3.54</v>
+        <v>3.12</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="AB27" t="n">
         <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.39</v>
+        <v>3.07</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.76</v>
+        <v>3.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="T28" t="n">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="U28" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V28" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.35</v>
       </c>
-      <c r="X28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4182,16 +4182,16 @@
         <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
         <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z29" t="n">
         <v>1.98</v>
@@ -4200,13 +4200,13 @@
         <v>2.88</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.37</v>
+        <v>2.54</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O30" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="T30" t="n">
         <v>2.95</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="X30" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="P31" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="R31" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="T31" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="U31" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="X31" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.16</v>
+        <v>1.74</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="AB31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC31" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.47</v>
+        <v>2.77</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
-        <v>4.08</v>
+        <v>3.46</v>
       </c>
       <c r="P32" t="n">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="U32" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>4</v>
+        <v>3.54</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,52 +4668,52 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.46</v>
+        <v>2.41</v>
       </c>
       <c r="M33" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="N33" t="n">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.63</v>
+        <v>3.45</v>
       </c>
       <c r="R33" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V33" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X33" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB33" t="n">
         <v>1.26</v>
@@ -4722,7 +4722,7 @@
         <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>2.54</v>
+        <v>3.02</v>
       </c>
       <c r="P34" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="T34" t="n">
-        <v>2.43</v>
+        <v>3.15</v>
       </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W34" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="X34" t="n">
-        <v>3.7</v>
+        <v>2.76</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="AB34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.38</v>
       </c>
-      <c r="AC34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.65</v>
+        <v>3.46</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="N35" t="n">
-        <v>5.5</v>
+        <v>2.02</v>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.75</v>
+        <v>2.63</v>
       </c>
       <c r="R35" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S35" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X35" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="Y35" t="n">
         <v>2</v>
       </c>
       <c r="Z35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA35" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AD35" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.38</v>
+        <v>1.26</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.99</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>3.64</v>
+        <v>3.98</v>
       </c>
       <c r="N36" t="n">
-        <v>2.17</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.57</v>
+        <v>3.62</v>
       </c>
       <c r="M37" t="n">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
       <c r="N37" t="n">
-        <v>5.5</v>
+        <v>1.96</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5316,10 +5316,10 @@
         <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -5349,7 +5349,7 @@
         <v>1.25</v>
       </c>
       <c r="X38" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="Y38" t="n">
         <v>1.83</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
         <v>1.48</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="M39" t="n">
-        <v>4.2</v>
+        <v>3.99</v>
       </c>
       <c r="N39" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.1</v>
+        <v>1.62</v>
       </c>
       <c r="M40" t="n">
         <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>1.73</v>
+        <v>4.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.3</v>
+        <v>1.99</v>
       </c>
       <c r="M41" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>1.71</v>
+        <v>3.47</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.62</v>
+        <v>2.99</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N42" t="n">
-        <v>4.75</v>
+        <v>2.17</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="M43" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.99</v>
+        <v>4.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N44" t="n">
-        <v>3.6</v>
+        <v>1.61</v>
       </c>
       <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z44" t="n">
         <v>2.45</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.03</v>
-      </c>
       <c r="AA44" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.22</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="T5" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.56</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AD5" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
         <v>4.3</v>
       </c>
-      <c r="N6" t="n">
-        <v>5.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1581,10 +1581,10 @@
         <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="P9" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="n">
         <v>10</v>
@@ -1599,16 +1599,16 @@
         <v>2.05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="n">
         <v>1.4</v>
@@ -1623,10 +1623,10 @@
         <v>1.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AH9" t="n">
         <v>4.35</v>
@@ -1710,10 +1710,10 @@
         <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
         <v>3.2</v>
@@ -1722,7 +1722,7 @@
         <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
@@ -1731,13 +1731,13 @@
         <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
         <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="n">
         <v>1.95</v>
@@ -1746,10 +1746,10 @@
         <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
         <v>1.83</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="M15" t="n">
         <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="T15" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V15" t="n">
         <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X15" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.1</v>
+        <v>4.51</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3387,52 +3387,52 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>2.73</v>
       </c>
       <c r="O24" t="n">
-        <v>3.02</v>
+        <v>2.72</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.84</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.96</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.47</v>
+        <v>2.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z26" t="n">
         <v>2</v>
       </c>
-      <c r="O26" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X26" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AA26" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="M27" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>6.51</v>
+        <v>2.4</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.75</v>
+        <v>3.05</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S27" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="X27" t="n">
-        <v>3.12</v>
+        <v>2.51</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.24</v>
+        <v>5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.07</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="U28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.26</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z28" t="n">
+      <c r="AC28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.09</v>
+        <v>3.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>3.19</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2.63</v>
+        <v>3.98</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>2.49</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
         <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X29" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.54</v>
+        <v>3.46</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="N30" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
         <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X30" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,58 +4410,58 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O31" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AD31" t="n">
         <v>2.14</v>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.77</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>3.44</v>
+        <v>3.85</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="O32" t="n">
-        <v>3.46</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.97</v>
+        <v>5.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X32" t="n">
-        <v>3.54</v>
+        <v>3.12</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.41</v>
+        <v>2.38</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
         <v>3.02</v>
       </c>
       <c r="P33" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T33" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W33" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X33" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.02</v>
+        <v>2.54</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.76</v>
+        <v>3.96</v>
       </c>
       <c r="R34" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="T34" t="n">
-        <v>3.15</v>
+        <v>2.43</v>
       </c>
       <c r="U34" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="X34" t="n">
-        <v>2.76</v>
+        <v>3.85</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="AB34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC34" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.46</v>
+        <v>2.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S35" t="n">
         <v>2.63</v>
       </c>
-      <c r="R35" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T35" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
         <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X35" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5064,34 +5064,34 @@
         <v>5.5</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y36" t="n">
         <v>1.89</v>
@@ -5100,16 +5100,16 @@
         <v>1.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="M37" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5316,10 +5316,10 @@
         <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -5352,7 +5352,7 @@
         <v>3.7</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Z38" t="n">
         <v>1.95</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.3</v>
+        <v>1.92</v>
       </c>
       <c r="M39" t="n">
-        <v>3.99</v>
+        <v>3.65</v>
       </c>
       <c r="N39" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.62</v>
+        <v>3.62</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="N40" t="n">
-        <v>4.75</v>
+        <v>1.96</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,77 +5700,77 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.99</v>
+        <v>4.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.99</v>
       </c>
       <c r="N41" t="n">
-        <v>3.47</v>
+        <v>1.71</v>
       </c>
       <c r="O41" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.95</v>
+        <v>2.15</v>
       </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S41" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T41" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="U41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.47</v>
       </c>
-      <c r="V41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W41" t="n">
+      <c r="AC41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.25</v>
       </c>
-      <c r="X41" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5838,34 +5838,34 @@
         <v>2.17</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y42" t="n">
         <v>1.68</v>
@@ -5874,16 +5874,16 @@
         <v>2.18</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,43 +5958,43 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.1</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
         <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>1.73</v>
+        <v>4.75</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y43" t="n">
         <v>1.68</v>
@@ -6003,16 +6003,16 @@
         <v>2.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6096,34 +6096,34 @@
         <v>1.61</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y44" t="n">
         <v>1.53</v>
@@ -6138,10 +6138,10 @@
         <v>1.62</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
         <v>2.3</v>
@@ -966,10 +966,10 @@
         <v>2.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AA4" t="n">
         <v>3.72</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.52</v>
       </c>
-      <c r="M5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>4.9</v>
+        <v>4.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.56</v>
+        <v>4.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M9" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>4.25</v>
+        <v>2.76</v>
       </c>
       <c r="T9" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>3.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>1.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,62 +1701,62 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>1.52</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="R10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.4</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>1.77</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>4.35</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
         <v>2.68</v>
       </c>
       <c r="P14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.32</v>
+        <v>3.65</v>
       </c>
       <c r="R14" t="n">
         <v>1.42</v>
@@ -2244,16 +2244,16 @@
         <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
         <v>1.28</v>
       </c>
       <c r="X14" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Y14" t="n">
         <v>1.95</v>
@@ -2268,10 +2268,10 @@
         <v>1.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y15" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Z15" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.51</v>
+        <v>3.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,77 +2475,77 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>4.32</v>
+        <v>4.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.28</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,62 +2733,62 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N18" t="n">
         <v>3.45</v>
       </c>
-      <c r="N18" t="n">
-        <v>1.9</v>
-      </c>
       <c r="O18" t="n">
-        <v>4.32</v>
+        <v>2.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.45</v>
+        <v>4.42</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.74</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.79</v>
+        <v>3.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD18" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O19" t="n">
         <v>3.2</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.7</v>
-      </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="T19" t="n">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X19" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="AB19" t="n">
         <v>1.19</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>2.96</v>
+        <v>2.29</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
         <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>2.88</v>
+        <v>4.65</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.5</v>
+        <v>2.28</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O23" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,77 +3636,77 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.62</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.77</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="P25" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>3.67</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.18</v>
+        <v>3.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="X25" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AC25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.51</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>3.46</v>
+        <v>3.02</v>
       </c>
       <c r="P26" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="T26" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="Y26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.05</v>
+        <v>2.43</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="X27" t="n">
-        <v>2.51</v>
+        <v>3.78</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="AA27" t="n">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,52 +4023,52 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.02</v>
       </c>
       <c r="O28" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.45</v>
+        <v>2.63</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB28" t="n">
         <v>1.26</v>
@@ -4077,7 +4077,7 @@
         <v>1.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3.75</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.49</v>
       </c>
       <c r="R29" t="n">
         <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X29" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.46</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="N30" t="n">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.63</v>
+        <v>5.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="T30" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.26</v>
+        <v>2.38</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M31" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="N31" t="n">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
         <v>2.63</v>
@@ -4443,28 +4443,28 @@
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X31" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AA31" t="n">
         <v>2.88</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>2.39</v>
       </c>
       <c r="M32" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P32" t="n">
         <v>2</v>
       </c>
-      <c r="P32" t="n">
-        <v>2.32</v>
-      </c>
       <c r="Q32" t="n">
-        <v>5.75</v>
+        <v>3.76</v>
       </c>
       <c r="R32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.38</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH32" t="n">
-        <v>2.38</v>
+        <v>1.54</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="M33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3.3</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.76</v>
       </c>
       <c r="R33" t="n">
         <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T33" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="U33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.31</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X33" t="n">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="AB33" t="n">
         <v>1.22</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>1.38</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O34" t="n">
-        <v>2.54</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.96</v>
+        <v>3.05</v>
       </c>
       <c r="R34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.32</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="M35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X35" t="n">
         <v>3.4</v>
       </c>
-      <c r="N35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.95</v>
-      </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="O36" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA36" t="n">
         <v>2.93</v>
       </c>
-      <c r="T36" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AB36" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M38" t="n">
         <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>3.47</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="R38" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T38" t="n">
         <v>2.48</v>
       </c>
       <c r="U38" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W38" t="n">
         <v>1.25</v>
       </c>
       <c r="X38" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AA38" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="N39" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="O39" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S39" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="T39" t="n">
         <v>2.48</v>
       </c>
       <c r="U39" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="V39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
         <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,77 +5571,77 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="M40" t="n">
-        <v>3.52</v>
+        <v>3.99</v>
       </c>
       <c r="N40" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="R40" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="S40" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="T40" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="U40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.47</v>
       </c>
-      <c r="V40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W40" t="n">
+      <c r="AC40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
         <v>1.25</v>
       </c>
-      <c r="X40" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="M41" t="n">
-        <v>3.99</v>
+        <v>3.52</v>
       </c>
       <c r="N41" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC41" t="n">
         <v>1.71</v>
       </c>
-      <c r="O41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AD41" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="N43" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="O43" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="P43" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R43" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="T43" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="U43" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W43" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X43" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -672,10 +672,10 @@
         <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="N2" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
         <v>1.75</v>
@@ -684,10 +684,10 @@
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.4</v>
+        <v>8.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
         <v>2.85</v>
@@ -723,7 +723,7 @@
         <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>5.17</v>
       </c>
       <c r="O4" t="n">
         <v>2.3</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
         <v>2.2</v>
@@ -1098,7 +1098,7 @@
         <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AA5" t="n">
         <v>2.38</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
         <v>1.96</v>
@@ -1203,10 +1203,10 @@
         <v>4.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
         <v>2.07</v>
@@ -1230,10 +1230,10 @@
         <v>2.43</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AC6" t="n">
         <v>1.56</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,13 +1323,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1338,37 +1338,37 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,13 +1452,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,62 +1572,62 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>1.52</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.88</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.21</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>4.35</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M10" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.52</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>4.25</v>
+        <v>2.67</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>2.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>3.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O13" t="n">
         <v>4.15</v>
@@ -2106,34 +2106,34 @@
         <v>2.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
         <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
-        <v>2.74</v>
+        <v>2.99</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AB13" t="n">
         <v>1.18</v>
@@ -2158,7 +2158,7 @@
         <v>1.62</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,62 +2217,62 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="Z14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AE14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,52 +2346,52 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>4.32</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="T15" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X15" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="Z15" t="n">
         <v>1.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.99</v>
+        <v>3.35</v>
       </c>
       <c r="AB15" t="n">
         <v>1.22</v>
@@ -2400,7 +2400,7 @@
         <v>1.79</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,65 +2471,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,77 +2733,77 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>3.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.28</v>
       </c>
-      <c r="X18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.68</v>
+        <v>1.29</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>3.57</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="P19" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.28</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X19" t="n">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>4.66</v>
+        <v>2.68</v>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>4.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="X20" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O21" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
         <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.79</v>
+        <v>3.55</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>6.1</v>
+        <v>4.65</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.29</v>
+        <v>1.73</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>3.62</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.67</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="T23" t="n">
-        <v>2.18</v>
+        <v>3.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="X23" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.24</v>
+        <v>1.69</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.51</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,28 +3507,28 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.78</v>
+        <v>4.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2.73</v>
+        <v>4.78</v>
       </c>
       <c r="O24" t="n">
-        <v>2.72</v>
+        <v>2.08</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="T24" t="n">
         <v>2.2</v>
@@ -3537,31 +3537,31 @@
         <v>1.62</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>2.27</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,77 +3636,77 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>3.04</v>
+        <v>2.72</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="T25" t="n">
-        <v>3.11</v>
+        <v>2.21</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="M26" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="T26" t="n">
         <v>2.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.42</v>
+        <v>1.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
+        <v>7</v>
+      </c>
+      <c r="O27" t="n">
         <v>2</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.98</v>
       </c>
       <c r="P27" t="n">
         <v>2.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.43</v>
+        <v>5.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X27" t="n">
-        <v>3.78</v>
+        <v>3.18</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.68</v>
+        <v>3.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.18</v>
+        <v>1.71</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.79</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.28</v>
+        <v>2.38</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.7</v>
+        <v>2.36</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y28" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2</v>
-      </c>
       <c r="Z28" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB28" t="n">
         <v>1.26</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.54</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="R29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.32</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="P30" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="R30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.38</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC30" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.09</v>
+        <v>3.66</v>
       </c>
       <c r="M31" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.63</v>
+        <v>4.05</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>2.43</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
         <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X31" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.39</v>
+        <v>2.09</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="O32" t="n">
-        <v>3.02</v>
+        <v>2.63</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="X32" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.82</v>
+        <v>2.88</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P33" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="R33" t="n">
         <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="T33" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="U33" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V33" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W33" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X33" t="n">
         <v>2.95</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="AB33" t="n">
         <v>1.22</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>1.38</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.07</v>
+        <v>3.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.05</v>
+        <v>2.61</v>
       </c>
       <c r="R34" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="T34" t="n">
-        <v>3.48</v>
+        <v>2.96</v>
       </c>
       <c r="U34" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="X34" t="n">
-        <v>2.51</v>
+        <v>3.15</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AA34" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4938,10 +4938,10 @@
         <v>3.46</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
         <v>1.35</v>
@@ -4974,7 +4974,7 @@
         <v>3.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC35" t="n">
         <v>1.73</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="O36" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X36" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="O37" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="P37" t="n">
         <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.24</v>
+        <v>3.95</v>
       </c>
       <c r="R37" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>4.05</v>
+        <v>3.76</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="n">
-        <v>3.47</v>
+        <v>1.73</v>
       </c>
       <c r="O38" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="P38" t="n">
         <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S38" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="U38" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.25</v>
       </c>
-      <c r="X38" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>2.57</v>
+        <v>1.98</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="R39" t="n">
         <v>1.35</v>
       </c>
       <c r="S39" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="T39" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U39" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
         <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA39" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="AB39" t="n">
         <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O40" t="n">
         <v>4.5</v>
@@ -5595,7 +5595,7 @@
         <v>3.45</v>
       </c>
       <c r="T40" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
         <v>1.56</v>
@@ -5610,13 +5610,13 @@
         <v>4.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AB40" t="n">
         <v>1.47</v>
@@ -5625,7 +5625,7 @@
         <v>1.61</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.62</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>1.96</v>
+        <v>5.62</v>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="P41" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.61</v>
+        <v>4.8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="T41" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="U41" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X41" t="n">
-        <v>3.76</v>
+        <v>3.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.26</v>
+        <v>2.28</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.99</v>
+        <v>1.57</v>
       </c>
       <c r="M42" t="n">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="N42" t="n">
-        <v>2.17</v>
+        <v>4.8</v>
       </c>
       <c r="O42" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.65</v>
+        <v>4.8</v>
       </c>
       <c r="R42" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
         <v>1.2</v>
       </c>
       <c r="X42" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.36</v>
+        <v>2.34</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U43" t="n">
         <v>1.57</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V43" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AC43" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="M44" t="n">
         <v>4.2</v>
       </c>
       <c r="N44" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O44" t="n">
         <v>4.4</v>
@@ -6114,10 +6114,10 @@
         <v>2.4</v>
       </c>
       <c r="U44" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
         <v>1.13</v>
@@ -6129,13 +6129,13 @@
         <v>1.53</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AA44" t="n">
         <v>2.3</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC44" t="n">
         <v>1.57</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -672,10 +672,10 @@
         <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>1.75</v>
@@ -687,10 +687,10 @@
         <v>8.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="T2" t="n">
         <v>2.7</v>
@@ -705,13 +705,13 @@
         <v>1.26</v>
       </c>
       <c r="X2" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
         <v>3.14</v>
@@ -739,7 +739,7 @@
         <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="O3" t="n">
         <v>2.6</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>5.17</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>2.3</v>
@@ -966,10 +966,10 @@
         <v>2.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
         <v>3.72</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.2</v>
+        <v>2.01</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>3.57</v>
       </c>
       <c r="O13" t="n">
-        <v>4.15</v>
+        <v>2.72</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.51</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>4.32</v>
+        <v>2.68</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.45</v>
+        <v>4.42</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,65 +2471,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.79</v>
+        <v>3.2</v>
       </c>
       <c r="M17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2.9</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O17" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.88</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="T17" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="U17" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
         <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.01</v>
+        <v>3.51</v>
       </c>
       <c r="M19" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.57</v>
+        <v>2.05</v>
       </c>
       <c r="O19" t="n">
-        <v>2.72</v>
+        <v>4.32</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="R19" t="n">
         <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="U19" t="n">
         <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X19" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
         <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="T22" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>4.65</v>
+        <v>6.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.35</v>
       </c>
-      <c r="M23" t="n">
+      <c r="Q23" t="n">
         <v>3</v>
       </c>
-      <c r="N23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.67</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="S23" t="n">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>3.11</v>
+        <v>2.21</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>2.27</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25</v>
+        <v>3.53</v>
       </c>
       <c r="N24" t="n">
-        <v>4.78</v>
+        <v>2.94</v>
       </c>
       <c r="O24" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X24" t="n">
         <v>4.4</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="Y24" t="n">
         <v>1.62</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.45</v>
-      </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
         <v>1.49</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.27</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="M25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA25" t="n">
         <v>3.7</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X25" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.51</v>
+        <v>1.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S26" t="n">
         <v>2.8</v>
       </c>
-      <c r="O26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T26" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.95</v>
+        <v>3.12</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>3.46</v>
       </c>
       <c r="P27" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.75</v>
+        <v>2.9</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
         <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Z27" t="n">
         <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AB27" t="n">
         <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.38</v>
+        <v>1.42</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.36</v>
+        <v>3.07</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="N28" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="R28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.42</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.36</v>
-      </c>
       <c r="X28" t="n">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.07</v>
+        <v>3.28</v>
       </c>
       <c r="M29" t="n">
-        <v>3.06</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>3.48</v>
+        <v>2.91</v>
       </c>
       <c r="U29" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>2.51</v>
+        <v>3.15</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AA29" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O30" t="n">
-        <v>2.54</v>
+        <v>2.99</v>
       </c>
       <c r="P30" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.95</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.43</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
         <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="X30" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.66</v>
+        <v>2.09</v>
       </c>
       <c r="M31" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q31" t="n">
         <v>3.6</v>
       </c>
-      <c r="N31" t="n">
-        <v>2</v>
-      </c>
-      <c r="O31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.43</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
         <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X31" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4542,58 +4542,58 @@
         <v>2.09</v>
       </c>
       <c r="M32" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="O32" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T32" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X32" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC32" t="n">
         <v>1.78</v>
       </c>
-      <c r="Z32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,62 +4668,62 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.38</v>
+        <v>3.66</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>3.02</v>
+        <v>4.05</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.76</v>
+        <v>2.43</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="T33" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="V33" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="X33" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD33" t="n">
         <v>2.17</v>
       </c>
-      <c r="Z33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.7</v>
+        <v>2.38</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P34" t="n">
         <v>2</v>
       </c>
-      <c r="O34" t="n">
-        <v>4</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Q34" t="n">
-        <v>2.61</v>
+        <v>3.76</v>
       </c>
       <c r="R34" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T34" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U34" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W34" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X34" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N35" t="n">
         <v>2.8</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.4</v>
-      </c>
       <c r="O35" t="n">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S35" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="T35" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="U35" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X35" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,62 +5055,62 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T36" t="n">
         <v>2.5</v>
       </c>
-      <c r="M36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O36" t="n">
-        <v>3</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="U36" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z36" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q36" t="n">
-        <v>3</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AD36" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.49</v>
+        <v>2.34</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,55 +5184,55 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="T37" t="n">
         <v>2.48</v>
       </c>
       <c r="U37" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
         <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC37" t="n">
         <v>1.63</v>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.1</v>
+        <v>1.58</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>1.73</v>
+        <v>5.62</v>
       </c>
       <c r="O38" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="P38" t="n">
         <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W38" t="n">
         <v>1.28</v>
       </c>
-      <c r="S38" t="n">
+      <c r="X38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA38" t="n">
         <v>3.4</v>
       </c>
-      <c r="T38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="AB38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.21</v>
       </c>
-      <c r="X38" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.2</v>
+        <v>2.28</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,34 +5442,34 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N39" t="n">
         <v>3.6</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.61</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V39" t="n">
         <v>1.03</v>
@@ -5478,41 +5478,41 @@
         <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,77 +5700,77 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>5.62</v>
+        <v>2.19</v>
       </c>
       <c r="O41" t="n">
-        <v>2.12</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.8</v>
+        <v>2.65</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S41" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X41" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="AB41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH41" t="n">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.57</v>
+        <v>3.6</v>
       </c>
       <c r="M42" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="N42" t="n">
-        <v>4.8</v>
+        <v>1.98</v>
       </c>
       <c r="O42" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.8</v>
+        <v>2.61</v>
       </c>
       <c r="R42" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S42" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="T42" t="n">
         <v>2.5</v>
       </c>
       <c r="U42" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="V42" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X42" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>2.34</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.19</v>
+        <v>1.62</v>
       </c>
       <c r="O43" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="R43" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T43" t="n">
         <v>2.4</v>
       </c>
       <c r="U43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.57</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.44</v>
       </c>
       <c r="AC43" t="n">
         <v>1.57</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="M44" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="O44" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="R44" t="n">
         <v>1.28</v>
       </c>
       <c r="S44" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T44" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W44" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X44" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK44"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,13 +684,13 @@
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
         <v>2.7</v>
@@ -723,7 +723,7 @@
         <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.56</v>
+        <v>5.13</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="T5" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>4.35</v>
+        <v>4.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1581,13 +1581,13 @@
         <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.2</v>
@@ -1596,10 +1596,10 @@
         <v>4.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -1608,19 +1608,19 @@
         <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="Y9" t="n">
         <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
         <v>1.91</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AH9" t="n">
         <v>4.35</v>
@@ -1710,7 +1710,7 @@
         <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
         <v>2.05</v>
@@ -1722,7 +1722,7 @@
         <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
@@ -1731,19 +1731,19 @@
         <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
         <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
         <v>3.88</v>
@@ -1752,10 +1752,10 @@
         <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,58 +2088,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.01</v>
+        <v>3.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.57</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
         <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
         <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AD13" t="n">
         <v>1.86</v>
@@ -2158,7 +2158,7 @@
         <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,77 +2217,77 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="M14" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T14" t="n">
         <v>3.2</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.41</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.42</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,31 +2475,31 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>4.44</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="U16" t="n">
         <v>1.33</v>
@@ -2508,28 +2508,28 @@
         <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X16" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.94</v>
+        <v>3.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AC16" t="n">
         <v>1.79</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,77 +2604,77 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>2.13</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>4.15</v>
+        <v>3.02</v>
       </c>
       <c r="P17" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>3.68</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.36</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.51</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>4.32</v>
+        <v>2.66</v>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.79</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>4.65</v>
+        <v>2.6</v>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="X20" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3129,52 +3129,52 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45951.625</v>
+        <v>45951.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="U23" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AC23" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
         <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="S24" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,77 +3636,77 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="M25" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3</v>
       </c>
-      <c r="N25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.67</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>3.11</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.69</v>
+        <v>2.23</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,77 +3765,77 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>3.26</v>
       </c>
       <c r="N26" t="n">
-        <v>7</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.75</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.38</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH26" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,62 +3894,62 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.8</v>
+        <v>3.78</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="O27" t="n">
-        <v>3.46</v>
+        <v>4.25</v>
       </c>
       <c r="P27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD27" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AE27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.07</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.06</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="P28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Z28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.28</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>2.15</v>
+        <v>7.2</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.72</v>
+        <v>5.75</v>
       </c>
       <c r="R29" t="n">
         <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
         <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.36</v>
+        <v>3.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>2.82</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="R30" t="n">
         <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T30" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X30" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB30" t="n">
         <v>1.26</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,62 +4410,62 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.09</v>
+        <v>2.88</v>
       </c>
       <c r="M31" t="n">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="N31" t="n">
-        <v>3.19</v>
+        <v>2.34</v>
       </c>
       <c r="O31" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>2.91</v>
       </c>
       <c r="R31" t="n">
         <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="Z31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.98</v>
       </c>
-      <c r="AA31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,62 +4539,62 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.09</v>
+        <v>3.09</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.34</v>
+        <v>2.37</v>
       </c>
       <c r="O32" t="n">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.96</v>
+        <v>3.05</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S32" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="U32" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="X32" t="n">
-        <v>3.85</v>
+        <v>2.61</v>
       </c>
       <c r="Y32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.74</v>
       </c>
-      <c r="Z32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.66</v>
+        <v>2.03</v>
       </c>
       <c r="M33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3.6</v>
       </c>
-      <c r="N33" t="n">
-        <v>2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.43</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S33" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U33" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X33" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4797,22 +4797,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O34" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="P34" t="n">
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.76</v>
+        <v>4.25</v>
       </c>
       <c r="R34" t="n">
         <v>1.41</v>
@@ -4833,25 +4833,25 @@
         <v>1.35</v>
       </c>
       <c r="X34" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AB34" t="n">
         <v>1.22</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>1.38</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.51</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD35" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC35" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5058,58 +5058,58 @@
         <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="N36" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
         <v>4.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X36" t="n">
         <v>3.3</v>
       </c>
-      <c r="T36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4</v>
-      </c>
       <c r="Y36" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="N37" t="n">
-        <v>2.7</v>
+        <v>1.71</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="P37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q37" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q37" t="n">
-        <v>3</v>
-      </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="S37" t="n">
-        <v>2.94</v>
+        <v>3.45</v>
       </c>
       <c r="T37" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="U37" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
       </c>
       <c r="W37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.25</v>
       </c>
-      <c r="X37" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.58</v>
+        <v>2.99</v>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="N38" t="n">
-        <v>5.62</v>
+        <v>2.17</v>
       </c>
       <c r="O38" t="n">
-        <v>2.12</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.8</v>
+        <v>2.65</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S38" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="T38" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="U38" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X38" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="AB38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH38" t="n">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="M39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S39" t="n">
         <v>3.5</v>
       </c>
-      <c r="N39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T39" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="V39" t="n">
         <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X39" t="n">
-        <v>3.76</v>
+        <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>2.33</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.8</v>
+        <v>1.19</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O40" t="n">
         <v>4.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="R40" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="U40" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X40" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC40" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AD40" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>2.01</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>3.21</v>
       </c>
       <c r="N41" t="n">
-        <v>2.19</v>
+        <v>3.21</v>
       </c>
       <c r="O41" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="P41" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S41" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="T41" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="U41" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.48</v>
+        <v>3.32</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,52 +5829,52 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.6</v>
+        <v>2.49</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="N42" t="n">
-        <v>1.98</v>
+        <v>2.69</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S42" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="T42" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="U42" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
         <v>1.25</v>
       </c>
       <c r="X42" t="n">
-        <v>3.8</v>
+        <v>3.61</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AB42" t="n">
         <v>1.36</v>
@@ -5883,7 +5883,7 @@
         <v>1.66</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N43" t="n">
         <v>4.75</v>
       </c>
-      <c r="M43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1.62</v>
-      </c>
       <c r="O43" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="P43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T43" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q43" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U43" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="N44" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1.73</v>
       </c>
-      <c r="O44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X44" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD44" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6167,6 +6167,135 @@
       </c>
       <c r="AK44" s="3" t="n">
         <v>45951.66666666666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Luxembourg National Division</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Swift Hesperange</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>45951.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5</v>
+        <v>2.98</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>4.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X2" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.22</v>
-      </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.14</v>
+        <v>5.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="N3" t="n">
-        <v>4.55</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.85</v>
+        <v>8.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="T3" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="V3" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.78</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.75</v>
+        <v>3.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.52</v>
       </c>
-      <c r="M5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.56</v>
+        <v>5.13</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M9" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>4.25</v>
+        <v>2.76</v>
       </c>
       <c r="T9" t="n">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>5.85</v>
+        <v>2.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>3.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>1.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="R10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.4</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="Z10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.06</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>4.35</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O13" t="n">
         <v>3.2</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.7</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.38</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X13" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.28</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>4.44</v>
+        <v>4.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="Y16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.97</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.02</v>
+        <v>4.44</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.68</v>
+        <v>2.45</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="U17" t="n">
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="X17" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AC17" t="n">
         <v>1.79</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.35</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>4.15</v>
+        <v>2.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Q18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.8</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="U18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,65 +2858,65 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="P20" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
         <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
         <v>1.28</v>
@@ -3036,16 +3036,16 @@
         <v>1.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3116,65 +3116,65 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45951.60416666666</v>
+        <v>45951.625</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="M22" t="n">
-        <v>4.25</v>
+        <v>3.63</v>
       </c>
       <c r="N22" t="n">
-        <v>4.78</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.68</v>
+        <v>3.55</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.45</v>
       </c>
-      <c r="Z22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AD22" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.27</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>4.65</v>
+        <v>5.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
         <v>2.38</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.28</v>
+        <v>2.61</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="R24" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="T24" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="U24" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.53</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>2.18</v>
+        <v>3.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="X25" t="n">
-        <v>4.4</v>
+        <v>3.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.23</v>
+        <v>1.63</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.39</v>
+        <v>1.9</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,58 +3765,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="X26" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
         <v>1.85</v>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.78</v>
+        <v>2.88</v>
       </c>
       <c r="M27" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="N27" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="O27" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.43</v>
+        <v>2.91</v>
       </c>
       <c r="R27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.3</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.23</v>
-      </c>
       <c r="X27" t="n">
-        <v>4.11</v>
+        <v>3.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>3.78</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>2.82</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
-        <v>3.04</v>
+        <v>4.25</v>
       </c>
       <c r="P28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="AA28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.42</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="N29" t="n">
-        <v>7.2</v>
+        <v>2.82</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>3.04</v>
       </c>
       <c r="P29" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.75</v>
+        <v>3.45</v>
       </c>
       <c r="R29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.38</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH29" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.55</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>7.2</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.84</v>
+        <v>5.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="T30" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
         <v>1.32</v>
       </c>
       <c r="X30" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.28</v>
+        <v>2.38</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N31" t="n">
         <v>2.88</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.34</v>
-      </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S31" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="T31" t="n">
         <v>2.95</v>
       </c>
       <c r="U31" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="X31" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.09</v>
+        <v>1.95</v>
       </c>
       <c r="M32" t="n">
-        <v>3.09</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="P32" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.05</v>
+        <v>4.11</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="T32" t="n">
-        <v>3.55</v>
+        <v>2.55</v>
       </c>
       <c r="U32" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="X32" t="n">
-        <v>2.61</v>
+        <v>3.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AA32" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.03</v>
+        <v>3.09</v>
       </c>
       <c r="M33" t="n">
-        <v>3.34</v>
+        <v>3.09</v>
       </c>
       <c r="N33" t="n">
-        <v>3.06</v>
+        <v>2.37</v>
       </c>
       <c r="O33" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="S33" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="X33" t="n">
-        <v>3.91</v>
+        <v>2.61</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.83</v>
+        <v>5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="M35" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3.6</v>
       </c>
-      <c r="N35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.11</v>
-      </c>
       <c r="R35" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="T35" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U35" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X35" t="n">
-        <v>3.85</v>
+        <v>3.91</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="O36" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
         <v>4.8</v>
       </c>
       <c r="R36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.4</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC36" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.3</v>
+        <v>2.49</v>
       </c>
       <c r="M37" t="n">
-        <v>3.99</v>
+        <v>3.38</v>
       </c>
       <c r="N37" t="n">
-        <v>1.71</v>
+        <v>2.69</v>
       </c>
       <c r="O37" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="T37" t="n">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="U37" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>4.33</v>
+        <v>3.61</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.99</v>
+        <v>2.01</v>
       </c>
       <c r="M38" t="n">
-        <v>3.64</v>
+        <v>3.21</v>
       </c>
       <c r="N38" t="n">
-        <v>2.17</v>
+        <v>3.21</v>
       </c>
       <c r="O38" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="P38" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S38" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="T38" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="U38" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X38" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.48</v>
+        <v>3.32</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q39" t="n">
         <v>4.8</v>
       </c>
-      <c r="M39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="O39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.13</v>
-      </c>
       <c r="R39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.28</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.17</v>
-      </c>
       <c r="X39" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>2.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.19</v>
+        <v>2.28</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="N40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC40" t="n">
         <v>1.73</v>
       </c>
-      <c r="O40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X40" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD40" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,77 +5700,77 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.01</v>
+        <v>4.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.21</v>
+        <v>3.99</v>
       </c>
       <c r="N41" t="n">
-        <v>3.21</v>
+        <v>1.71</v>
       </c>
       <c r="O41" t="n">
-        <v>2.64</v>
+        <v>4.5</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="R41" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="S41" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="T41" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA41" t="n">
         <v>2.48</v>
       </c>
-      <c r="U41" t="n">
+      <c r="AB41" t="n">
         <v>1.47</v>
       </c>
-      <c r="V41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W41" t="n">
+      <c r="AC41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.25</v>
       </c>
-      <c r="X41" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.49</v>
+        <v>2.99</v>
       </c>
       <c r="M42" t="n">
-        <v>3.38</v>
+        <v>3.64</v>
       </c>
       <c r="N42" t="n">
-        <v>2.69</v>
+        <v>2.17</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="R42" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="U42" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X42" t="n">
-        <v>3.61</v>
+        <v>4.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AA42" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AB42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.45</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.62</v>
       </c>
-      <c r="M43" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X43" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC43" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>2.33</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.2</v>
+        <v>1.19</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="M44" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X44" t="n">
         <v>4</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.78</v>
-      </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6167,135 +6167,6 @@
       </c>
       <c r="AK44" s="3" t="n">
         <v>45951.66666666666</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>45951</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Luxembourg National Division</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Swift Hesperange</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Racing</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="N45" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="O45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK45" s="3" t="n">
-        <v>45951.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK44"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="N2" t="n">
-        <v>4.55</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.85</v>
+        <v>8.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="X2" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.78</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.75</v>
+        <v>3.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.22</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.14</v>
+        <v>5.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
         <v>2.3</v>
@@ -966,10 +966,10 @@
         <v>2.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AA4" t="n">
         <v>3.72</v>
@@ -978,7 +978,7 @@
         <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
         <v>1.72</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
         <v>2.2</v>
@@ -1089,16 +1089,16 @@
         <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
         <v>4.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AA5" t="n">
         <v>2.38</v>
@@ -1107,7 +1107,7 @@
         <v>1.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AD5" t="n">
         <v>2.08</v>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="P6" t="n">
         <v>2.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.13</v>
+        <v>4.7</v>
       </c>
       <c r="R6" t="n">
         <v>1.22</v>
@@ -1218,28 +1218,28 @@
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>4.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
         <v>2.43</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AC6" t="n">
         <v>1.56</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AH6" t="n">
         <v>2.41</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>4.35</v>
       </c>
       <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y13" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z13" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2217,19 +2217,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
         <v>4.38</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
         <v>2.88</v>
@@ -2256,13 +2256,13 @@
         <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AB14" t="n">
         <v>1.14</v>
@@ -2287,7 +2287,7 @@
         <v>1.56</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,65 +2342,65 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,28 +2475,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.15</v>
+        <v>2.68</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.62</v>
       </c>
       <c r="T16" t="n">
         <v>3.18</v>
@@ -2505,31 +2505,31 @@
         <v>1.29</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,77 +2604,77 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4.44</v>
+        <v>4.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="T17" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="U17" t="n">
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.27</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,19 +2733,19 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>2.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
         <v>4</v>
@@ -2769,13 +2769,13 @@
         <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AA18" t="n">
         <v>3.5</v>
@@ -2784,10 +2784,10 @@
         <v>1.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,65 +2858,65 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,62 +2991,62 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="T20" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="Z20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA20" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>4.78</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.08</v>
+        <v>3.04</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>2.96</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="X21" t="n">
-        <v>6.1</v>
+        <v>3.11</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.7</v>
+        <v>1.69</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.21</v>
+        <v>1.51</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.22</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>4.78</v>
       </c>
       <c r="O22" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="P22" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V22" t="n">
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="U23" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Z23" t="n">
         <v>2.38</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.61</v>
+        <v>2.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z24" t="n">
         <v>2.5</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AA24" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.25</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Q25" t="n">
-        <v>3.68</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>3.11</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>3.11</v>
+        <v>5.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.7</v>
+        <v>2.61</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3765,16 +3765,16 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P26" t="n">
         <v>2.18</v>
@@ -3792,7 +3792,7 @@
         <v>2.91</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
         <v>1</v>
@@ -3804,7 +3804,7 @@
         <v>3.15</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
         <v>1.73</v>
@@ -3816,10 +3816,10 @@
         <v>1.26</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3894,22 +3894,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O27" t="n">
         <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="R27" t="n">
         <v>1.35</v>
@@ -3933,10 +3933,10 @@
         <v>3.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
         <v>3.35</v>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="n">
         <v>1.42</v>
@@ -4023,16 +4023,16 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="M28" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="O28" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="P28" t="n">
         <v>2.32</v>
@@ -4041,7 +4041,7 @@
         <v>2.43</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
         <v>3.3</v>
@@ -4050,7 +4050,7 @@
         <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
         <v>1</v>
@@ -4059,7 +4059,7 @@
         <v>1.23</v>
       </c>
       <c r="X28" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="Y28" t="n">
         <v>1.75</v>
@@ -4068,16 +4068,16 @@
         <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AB28" t="n">
         <v>1.42</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
         <v>1.25</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="T29" t="n">
         <v>2.95</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W29" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.62</v>
+        <v>3.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>1.38</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.75</v>
+        <v>4.11</v>
       </c>
       <c r="R30" t="n">
         <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
         <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="X30" t="n">
-        <v>3.12</v>
+        <v>3.85</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="M31" t="n">
-        <v>3.26</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>5.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>2.63</v>
+        <v>2.93</v>
       </c>
       <c r="T31" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="X31" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.95</v>
+        <v>3.24</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P32" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.38</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4668,16 +4668,16 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="M33" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="N33" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P33" t="n">
         <v>1.98</v>
@@ -4698,31 +4698,31 @@
         <v>1.25</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X33" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA33" t="n">
         <v>5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>1.6</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.37</v>
+        <v>2.09</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="O34" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T34" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="U34" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V34" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W34" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="X34" t="n">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="Z34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC34" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AD34" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,62 +4926,62 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="U35" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="X35" t="n">
-        <v>3.91</v>
+        <v>3.15</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="Z35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD35" t="n">
         <v>1.9</v>
       </c>
-      <c r="AA35" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,43 +5055,43 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>4.3</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="N36" t="n">
-        <v>4.75</v>
+        <v>1.71</v>
       </c>
       <c r="O36" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X36" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Y36" t="n">
         <v>1.68</v>
@@ -5100,16 +5100,16 @@
         <v>2.18</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.2</v>
+        <v>1.16</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.49</v>
+        <v>1.62</v>
       </c>
       <c r="M37" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>2.69</v>
+        <v>4.75</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AA37" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.01</v>
+        <v>2.99</v>
       </c>
       <c r="M38" t="n">
-        <v>3.21</v>
+        <v>3.64</v>
       </c>
       <c r="N38" t="n">
-        <v>3.21</v>
+        <v>2.17</v>
       </c>
       <c r="O38" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.1</v>
+        <v>2.65</v>
       </c>
       <c r="R38" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="S38" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="T38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA38" t="n">
         <v>2.48</v>
       </c>
-      <c r="U38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.32</v>
-      </c>
       <c r="AB38" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.57</v>
+        <v>4.1</v>
       </c>
       <c r="M39" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>5.5</v>
+        <v>1.73</v>
       </c>
       <c r="O39" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.8</v>
+        <v>2.22</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="U39" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="V39" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W39" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="X39" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.28</v>
+        <v>1.2</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.3</v>
+        <v>1.57</v>
       </c>
       <c r="M41" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="N41" t="n">
-        <v>1.71</v>
+        <v>5.5</v>
       </c>
       <c r="O41" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="P41" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="T41" t="n">
-        <v>2.39</v>
+        <v>2.92</v>
       </c>
       <c r="U41" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X41" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.16</v>
+        <v>2.28</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.99</v>
+        <v>2.05</v>
       </c>
       <c r="M42" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>2.17</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="R42" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X42" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.48</v>
+        <v>3.32</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.39</v>
       </c>
       <c r="N44" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O44" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="T44" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="U44" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X44" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6167,6 +6167,135 @@
       </c>
       <c r="AK44" s="3" t="n">
         <v>45951.66666666666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Luxembourg National Division</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Swift Hesperange</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>45951.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -672,10 +672,10 @@
         <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1.75</v>
@@ -687,10 +687,10 @@
         <v>8.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="T2" t="n">
         <v>2.7</v>
@@ -705,13 +705,13 @@
         <v>1.26</v>
       </c>
       <c r="X2" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AA2" t="n">
         <v>3.14</v>
@@ -723,7 +723,7 @@
         <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
         <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.85</v>
+        <v>5.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
         <v>3.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
         <v>2.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -930,7 +930,7 @@
         <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
         <v>4.75</v>
@@ -978,7 +978,7 @@
         <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD4" t="n">
         <v>1.72</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.62</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>1.51</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="Z9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.06</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>4.35</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>2.63</v>
       </c>
       <c r="M10" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>4.25</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>5.85</v>
+        <v>2.96</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>3.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>3.17</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
         <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.35</v>
+        <v>3.76</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AC13" t="n">
         <v>1.79</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.54</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>4.38</v>
+        <v>2.68</v>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>4.42</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="X14" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.33</v>
+        <v>3.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
         <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T16" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="U16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
         <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2607,58 +2607,58 @@
         <v>3.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.39</v>
+        <v>2.74</v>
       </c>
       <c r="T17" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="X17" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>3.54</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.6</v>
+        <v>4.38</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.42</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X18" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N19" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="T19" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="X19" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X20" t="n">
         <v>2.74</v>
       </c>
-      <c r="M20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.77</v>
-      </c>
       <c r="Y20" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.04</v>
+        <v>2.79</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>3.11</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.69</v>
+        <v>2.23</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.7</v>
+        <v>2.61</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.6</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>4.79</v>
       </c>
       <c r="R23" t="n">
         <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>4.65</v>
+        <v>6</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC23" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AD23" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,34 +3507,34 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="M24" t="n">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="V24" t="n">
         <v>1.02</v>
@@ -3543,19 +3543,19 @@
         <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
         <v>1.45</v>
@@ -3577,7 +3577,7 @@
         <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="M25" t="n">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="N25" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.18</v>
+        <v>2.96</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="X25" t="n">
-        <v>5.2</v>
+        <v>2.88</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.38</v>
+        <v>1.69</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.61</v>
+        <v>3.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.39</v>
+        <v>1.9</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.15</v>
       </c>
-      <c r="M26" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.91</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W26" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T27" t="n">
         <v>3</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X27" t="n">
         <v>2.95</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.4</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Z27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD27" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4029,49 +4029,49 @@
         <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="O28" t="n">
         <v>4.33</v>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
         <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
         <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
         <v>4</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Z28" t="n">
         <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AC28" t="n">
         <v>1.63</v>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P29" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="T29" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V29" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
         <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.95</v>
+        <v>3.24</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="P30" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.11</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="T30" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X30" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Y30" t="n">
         <v>1.74</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,31 +4410,31 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.75</v>
+        <v>2.96</v>
       </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U31" t="n">
         <v>1.37</v>
@@ -4443,28 +4443,28 @@
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X31" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z31" t="n">
         <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.38</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,62 +4539,62 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P32" t="n">
         <v>2.1</v>
       </c>
-      <c r="M32" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2</v>
-      </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X32" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.87</v>
       </c>
-      <c r="AD32" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="M33" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
-        <v>3.98</v>
+        <v>2.6</v>
       </c>
       <c r="P33" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.05</v>
+        <v>4.11</v>
       </c>
       <c r="R33" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="T33" t="n">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="U33" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V33" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AA33" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.09</v>
+        <v>3.15</v>
       </c>
       <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA34" t="n">
         <v>3.5</v>
       </c>
-      <c r="N34" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AB34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>3.04</v>
+        <v>3.92</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="T35" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W35" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X35" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.3</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="N36" t="n">
-        <v>1.71</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="P36" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="T36" t="n">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="U36" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X36" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.16</v>
+        <v>2.28</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,43 +5184,43 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.62</v>
+        <v>2.99</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N37" t="n">
-        <v>4.75</v>
+        <v>2.17</v>
       </c>
       <c r="O37" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.8</v>
+        <v>2.65</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Y37" t="n">
         <v>1.68</v>
@@ -5229,16 +5229,16 @@
         <v>2.18</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,43 +5313,43 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.99</v>
+        <v>4.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="O38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S38" t="n">
         <v>3.4</v>
       </c>
-      <c r="P38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T38" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="U38" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X38" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="Y38" t="n">
         <v>1.68</v>
@@ -5358,16 +5358,16 @@
         <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N39" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="O39" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P39" t="n">
         <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="R39" t="n">
         <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T39" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="V39" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,77 +5571,77 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.62</v>
+        <v>2.01</v>
       </c>
       <c r="M40" t="n">
-        <v>3.52</v>
+        <v>3.21</v>
       </c>
       <c r="N40" t="n">
-        <v>1.96</v>
+        <v>3.21</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="P40" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S40" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T40" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="U40" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V40" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
         <v>1.22</v>
       </c>
-      <c r="X40" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="Y40" t="n">
+      <c r="AH40" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M41" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="O41" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
         <v>4.8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="T41" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="U41" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X41" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.05</v>
+        <v>4.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.99</v>
       </c>
       <c r="N42" t="n">
-        <v>3.5</v>
+        <v>1.71</v>
       </c>
       <c r="O42" t="n">
-        <v>2.64</v>
+        <v>4.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T42" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA42" t="n">
         <v>2.48</v>
       </c>
-      <c r="U42" t="n">
+      <c r="AB42" t="n">
         <v>1.47</v>
       </c>
-      <c r="V42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W42" t="n">
+      <c r="AC42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.25</v>
       </c>
-      <c r="X42" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.8</v>
+        <v>3.62</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="N43" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="O43" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.13</v>
+        <v>2.56</v>
       </c>
       <c r="R43" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="T43" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="U43" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="V43" t="n">
         <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X43" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6090,28 +6090,28 @@
         <v>2.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q44" t="n">
         <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S44" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="T44" t="n">
-        <v>2.48</v>
+        <v>2.73</v>
       </c>
       <c r="U44" t="n">
         <v>1.4</v>
@@ -6120,22 +6120,22 @@
         <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X44" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AA44" t="n">
         <v>3</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC44" t="n">
         <v>1.66</v>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.25</v>
+        <v>5.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S3" t="n">
         <v>2.2</v>
@@ -828,7 +828,7 @@
         <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
         <v>1.58</v>
@@ -837,7 +837,7 @@
         <v>2.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Z3" t="n">
         <v>1.37</v>
@@ -846,13 +846,13 @@
         <v>5.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>2.3</v>
@@ -948,13 +948,13 @@
         <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
@@ -963,13 +963,13 @@
         <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
         <v>3.72</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.52</v>
       </c>
-      <c r="M5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.56</v>
+        <v>4.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>2.82</v>
       </c>
       <c r="M9" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.51</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>8.300000000000001</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>4.25</v>
+        <v>2.68</v>
       </c>
       <c r="T9" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>3.17</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>3.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.06</v>
+        <v>1.52</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>1.17</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>16</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>1.52</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>3.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.4</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.88</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>4.75</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="X13" t="n">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.68</v>
+        <v>4.47</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.42</v>
+        <v>2.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="X14" t="n">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.94</v>
+        <v>3.76</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,65 +2342,65 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,77 +2475,77 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="P16" t="n">
         <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>4.42</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="X16" t="n">
-        <v>3.03</v>
+        <v>2.74</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Z16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.69</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.54</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>4.38</v>
+        <v>2.65</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.88</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Y18" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,77 +2862,77 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="U19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.28</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,28 +2991,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="P20" t="n">
         <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="T20" t="n">
         <v>3.18</v>
@@ -3027,25 +3027,25 @@
         <v>1.35</v>
       </c>
       <c r="X20" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA20" t="n">
         <v>3.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
         <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
         <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X21" t="n">
         <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.61</v>
+        <v>2.41</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3.76</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.45</v>
       </c>
-      <c r="AC22" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AD22" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.76</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.33</v>
+        <v>2.61</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3636,34 +3636,34 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.67</v>
+        <v>3.84</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S25" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
         <v>2.96</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
@@ -3675,16 +3675,16 @@
         <v>2.88</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC25" t="n">
         <v>1.79</v>
@@ -3706,7 +3706,7 @@
         <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.25</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA26" t="n">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="M27" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P27" t="n">
         <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X27" t="n">
         <v>3</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.95</v>
-      </c>
       <c r="Y27" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.1</v>
+        <v>2.08</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="O28" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="P28" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>4.11</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="N29" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P29" t="n">
         <v>2.1</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q29" t="n">
-        <v>5.8</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
         <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.24</v>
+        <v>3.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.22</v>
+        <v>1.46</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.09</v>
+        <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>3.21</v>
+        <v>1.81</v>
       </c>
       <c r="O30" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
         <v>1.22</v>
       </c>
       <c r="X30" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.83</v>
+        <v>2.61</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,62 +4410,62 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>3.92</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="R31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.3</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W31" t="n">
         <v>1.37</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.31</v>
-      </c>
       <c r="X31" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="Z31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2</v>
-      </c>
       <c r="AE31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="M32" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T32" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W32" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X32" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="P33" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.11</v>
+        <v>3.45</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X33" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA34" t="n">
         <v>3</v>
       </c>
-      <c r="N34" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="AB34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.33</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.05</v>
+        <v>1.63</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="O35" t="n">
-        <v>3.92</v>
+        <v>2.1</v>
       </c>
       <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Y35" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.27</v>
-      </c>
       <c r="Z35" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.4</v>
+        <v>3.24</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.33</v>
+        <v>2.22</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M36" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>5.5</v>
+        <v>2.61</v>
       </c>
       <c r="O36" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
         <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T36" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U36" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
         <v>1.28</v>
       </c>
       <c r="X36" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.28</v>
+        <v>1.48</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.99</v>
+        <v>1.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>2.17</v>
+        <v>5.75</v>
       </c>
       <c r="O37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA37" t="n">
         <v>3.4</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.1</v>
+        <v>4.49</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="N38" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="O38" t="n">
         <v>4.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="R38" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S38" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T38" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="U38" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="V38" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W38" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X38" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="M39" t="n">
         <v>4.2</v>
       </c>
       <c r="N39" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="O39" t="n">
         <v>4.4</v>
@@ -5460,10 +5460,10 @@
         <v>2.13</v>
       </c>
       <c r="R39" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S39" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T39" t="n">
         <v>2.4</v>
@@ -5472,7 +5472,7 @@
         <v>1.6</v>
       </c>
       <c r="V39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
         <v>1.17</v>
@@ -5484,13 +5484,13 @@
         <v>1.53</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AA39" t="n">
         <v>2.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC39" t="n">
         <v>1.57</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,77 +5571,77 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="M40" t="n">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>3.21</v>
+        <v>2.2</v>
       </c>
       <c r="O40" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S40" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA40" t="n">
         <v>2.48</v>
       </c>
-      <c r="U40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W40" t="n">
+      <c r="AB40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
         <v>1.25</v>
       </c>
-      <c r="X40" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.62</v>
+        <v>3.98</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>4.75</v>
+        <v>1.96</v>
       </c>
       <c r="O41" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.8</v>
+        <v>2.56</v>
       </c>
       <c r="R41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.33</v>
       </c>
-      <c r="S41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AC41" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.34</v>
+        <v>1.26</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.3</v>
+        <v>1.63</v>
       </c>
       <c r="M42" t="n">
-        <v>3.99</v>
+        <v>4.05</v>
       </c>
       <c r="N42" t="n">
-        <v>1.71</v>
+        <v>5.15</v>
       </c>
       <c r="O42" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="P42" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="R42" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="U42" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.18</v>
       </c>
-      <c r="X42" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.16</v>
+        <v>2.2</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,77 +5958,77 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.62</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>1.96</v>
+        <v>3.75</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="P43" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.56</v>
+        <v>4.15</v>
       </c>
       <c r="R43" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S43" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="T43" t="n">
         <v>2.63</v>
       </c>
       <c r="U43" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V43" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
         <v>1.25</v>
       </c>
-      <c r="X43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AH43" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>2.61</v>
+        <v>1.7</v>
       </c>
       <c r="O44" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.73</v>
+        <v>2.35</v>
       </c>
       <c r="U44" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V44" t="n">
         <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X44" t="n">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S2" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1.37</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AA2" t="n">
-        <v>3.14</v>
+        <v>5.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.85</v>
+        <v>8.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="T3" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="V3" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.78</v>
+        <v>1.91</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.37</v>
+        <v>1.84</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.4</v>
+        <v>3.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.85</v>
+        <v>3.15</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.56</v>
+        <v>4.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="T5" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.52</v>
       </c>
-      <c r="M6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.63</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.41</v>
+        <v>2.06</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.82</v>
+        <v>1.17</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>16</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>1.52</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>3.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z9" t="n">
-        <v>1.66</v>
+        <v>2.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.88</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.52</v>
+        <v>1.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>4.75</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.17</v>
+        <v>2.82</v>
       </c>
       <c r="M10" t="n">
-        <v>8.300000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.52</v>
       </c>
-      <c r="P10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH10" t="n">
-        <v>4.75</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.65</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.48</v>
-      </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="U13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.28</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.45</v>
-      </c>
       <c r="X13" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,77 +2217,77 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="O14" t="n">
-        <v>4.47</v>
+        <v>3.48</v>
       </c>
       <c r="P14" t="n">
         <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.41</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,65 +2342,65 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.68</v>
+        <v>4.38</v>
       </c>
       <c r="P16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X18" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>4.47</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.98</v>
+        <v>2.56</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
         <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X19" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA19" t="n">
         <v>3.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.39</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.62</v>
+        <v>4.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>4.78</v>
       </c>
       <c r="O21" t="n">
-        <v>2.85</v>
+        <v>2.08</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>4.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.19</v>
       </c>
-      <c r="X21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.54</v>
+        <v>2.23</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="R22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.25</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>4.78</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.79</v>
+        <v>3.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
         <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.68</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.23</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>3.62</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="P25" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.84</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.45</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC25" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="N26" t="n">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6</v>
+        <v>3.16</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
-        <v>3.76</v>
+        <v>2.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.83</v>
+        <v>3.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.15</v>
+        <v>2.41</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="O27" t="n">
-        <v>3.9</v>
+        <v>3.04</v>
       </c>
       <c r="P27" t="n">
         <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="R27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.36</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4023,34 +4023,34 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
         <v>3.4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
         <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
@@ -4059,22 +4059,22 @@
         <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
         <v>3.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD28" t="n">
         <v>1.95</v>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="M29" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="R29" t="n">
         <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U29" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W29" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X29" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AB29" t="n">
         <v>1.22</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>1.81</v>
+        <v>7.2</v>
       </c>
       <c r="O30" t="n">
-        <v>4.33</v>
+        <v>2.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.3</v>
+        <v>5.89</v>
       </c>
       <c r="R30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.32</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X30" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.61</v>
+        <v>3.24</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.23</v>
+        <v>2.22</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="O31" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="P31" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.05</v>
+        <v>2.71</v>
       </c>
       <c r="R31" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>2.48</v>
+        <v>2.91</v>
       </c>
       <c r="T31" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="U31" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V31" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X31" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,62 +4539,62 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="O32" t="n">
-        <v>2.85</v>
+        <v>3.46</v>
       </c>
       <c r="P32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,77 +4668,77 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.41</v>
+        <v>3.78</v>
       </c>
       <c r="M33" t="n">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="O33" t="n">
-        <v>3.04</v>
+        <v>4.4</v>
       </c>
       <c r="P33" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="AA33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.42</v>
       </c>
-      <c r="S33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,62 +4797,62 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q34" t="n">
         <v>3</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.96</v>
-      </c>
       <c r="R34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U34" t="n">
         <v>1.3</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.37</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.31</v>
-      </c>
       <c r="X34" t="n">
-        <v>3.35</v>
+        <v>2.81</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Z34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2</v>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.63</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD35" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.22</v>
+        <v>1.71</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N36" t="n">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="O36" t="n">
         <v>3.1</v>
@@ -5088,16 +5088,16 @@
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X36" t="n">
         <v>3.38</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AA36" t="n">
         <v>3</v>
@@ -5109,7 +5109,7 @@
         <v>1.66</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH36" t="n">
         <v>1.48</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="N37" t="n">
-        <v>5.75</v>
+        <v>5.15</v>
       </c>
       <c r="O37" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q37" t="n">
         <v>4.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AC37" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.49</v>
+        <v>4.6</v>
       </c>
       <c r="M38" t="n">
-        <v>4.18</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O38" t="n">
         <v>4.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="U38" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X38" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.75</v>
+        <v>2.83</v>
       </c>
       <c r="M39" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N39" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="O39" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T39" t="n">
         <v>2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X39" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AC39" t="n">
         <v>1.57</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.83</v>
+        <v>3.98</v>
       </c>
       <c r="M40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X40" t="n">
         <v>3.7</v>
       </c>
-      <c r="N40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X40" t="n">
-        <v>4.33</v>
-      </c>
       <c r="Y40" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.48</v>
+        <v>2.91</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,77 +5700,77 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N41" t="n">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X41" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z41" t="n">
         <v>2.37</v>
       </c>
-      <c r="Q41" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W41" t="n">
+      <c r="AA41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.25</v>
       </c>
-      <c r="X41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>5.15</v>
+        <v>5.75</v>
       </c>
       <c r="O42" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="P42" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
         <v>4.8</v>
       </c>
       <c r="R42" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S42" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X42" t="n">
         <v>3.3</v>
       </c>
-      <c r="T42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.9</v>
-      </c>
       <c r="Y42" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="N43" t="n">
-        <v>3.75</v>
+        <v>3.21</v>
       </c>
       <c r="O43" t="n">
         <v>2.64</v>
@@ -5979,7 +5979,7 @@
         <v>1.38</v>
       </c>
       <c r="S43" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="T43" t="n">
         <v>2.63</v>
@@ -5988,31 +5988,31 @@
         <v>1.41</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W43" t="n">
         <v>1.3</v>
       </c>
       <c r="X43" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AA43" t="n">
         <v>3.32</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.6</v>
+        <v>4.49</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="N44" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O44" t="n">
         <v>4.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S44" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T44" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="U44" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X44" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -684,22 +684,22 @@
         <v>1.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.85</v>
+        <v>5.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="T2" t="n">
         <v>3.95</v>
       </c>
       <c r="U2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
         <v>1.58</v>
@@ -708,13 +708,13 @@
         <v>2.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AB2" t="n">
         <v>1.07</v>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45951.45833333334</v>
@@ -801,31 +801,31 @@
         <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="N3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.4</v>
+        <v>10.61</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
         <v>2.66</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
@@ -834,13 +834,13 @@
         <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
         <v>3.14</v>
@@ -849,7 +849,7 @@
         <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD3" t="n">
         <v>1.44</v>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
         <v>3.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45951.45833333334</v>
@@ -936,34 +936,34 @@
         <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
         <v>4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
         <v>2.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Y4" t="n">
         <v>2.05</v>
@@ -978,7 +978,7 @@
         <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
         <v>1.72</v>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45951.47916666666</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.41</v>
+        <v>2.06</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45951.5</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.06</v>
+        <v>2.41</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45951.5</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1338,37 +1338,37 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,13 +1452,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="N9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
         <v>1.52</v>
       </c>
       <c r="P9" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
         <v>2.11</v>
@@ -1608,19 +1608,19 @@
         <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
         <v>1.91</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AH9" t="n">
         <v>4.75</v>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
         <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
         <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="AB10" t="n">
         <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
         <v>1.44</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="M14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X14" t="n">
         <v>3.1</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.59</v>
-      </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,65 +2342,65 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2484,22 +2484,22 @@
         <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>4.38</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
         <v>2.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="T16" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
         <v>1.26</v>
@@ -2526,10 +2526,10 @@
         <v>1.14</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="P17" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.98</v>
-      </c>
       <c r="Q17" t="n">
-        <v>4.42</v>
+        <v>2.91</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="T17" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
         <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
         <v>2.74</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.98</v>
+        <v>2.56</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X18" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.45</v>
       </c>
-      <c r="N19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="O19" t="n">
-        <v>4.47</v>
+        <v>2.68</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.56</v>
+        <v>4.56</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="T19" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="X19" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.76</v>
+        <v>3.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
         <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.15</v>
+        <v>3.64</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3123,58 +3123,58 @@
         <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.79</v>
+        <v>5.01</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
         <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>3.04</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
         <v>3.84</v>
@@ -3270,13 +3270,13 @@
         <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
@@ -3297,7 +3297,7 @@
         <v>3.42</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AC22" t="n">
         <v>1.79</v>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
         <v>1.51</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.76</v>
+        <v>3.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="U23" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
         <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.38</v>
       </c>
-      <c r="AA23" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="R24" t="n">
         <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="AB24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AD24" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.39</v>
+        <v>1.98</v>
       </c>
       <c r="M25" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="O25" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="U25" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>4.4</v>
+        <v>5.09</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="M26" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="O26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S26" t="n">
         <v>3.1</v>
       </c>
-      <c r="P26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T26" t="n">
-        <v>3.16</v>
+        <v>2.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.95</v>
+        <v>2.78</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.42</v>
+        <v>1.76</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="O27" t="n">
-        <v>3.04</v>
+        <v>2.55</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X27" t="n">
         <v>3.45</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.94</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>3.78</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>4.15</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.16</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>2.82</v>
+        <v>2.47</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>3.33</v>
+        <v>3.85</v>
       </c>
       <c r="Y28" t="n">
         <v>1.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.37</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>2.99</v>
+        <v>7.2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="P29" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AD29" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,77 +4281,77 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>3.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>7.2</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.89</v>
+        <v>2.68</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="T30" t="n">
         <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X30" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>2.22</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.55</v>
+        <v>2.37</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="N31" t="n">
-        <v>1.97</v>
+        <v>2.99</v>
       </c>
       <c r="O31" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y31" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.97</v>
-      </c>
       <c r="Z31" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N32" t="n">
         <v>2.88</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.34</v>
-      </c>
       <c r="O32" t="n">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.7</v>
+        <v>3.48</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X32" t="n">
         <v>2.8</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.35</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AA32" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.78</v>
+        <v>2.41</v>
       </c>
       <c r="M33" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>1.9</v>
+        <v>2.82</v>
       </c>
       <c r="O33" t="n">
-        <v>4.4</v>
+        <v>3.04</v>
       </c>
       <c r="P33" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="R33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.32</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X33" t="n">
-        <v>3.85</v>
+        <v>2.89</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.6</v>
+        <v>3.62</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4815,16 +4815,16 @@
         <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S34" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T34" t="n">
         <v>3.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V34" t="n">
         <v>1.03</v>
@@ -4833,7 +4833,7 @@
         <v>1.37</v>
       </c>
       <c r="X34" t="n">
-        <v>2.81</v>
+        <v>2.68</v>
       </c>
       <c r="Y34" t="n">
         <v>2.35</v>
@@ -4845,13 +4845,13 @@
         <v>4.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N35" t="n">
-        <v>3.06</v>
+        <v>2.34</v>
       </c>
       <c r="O35" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X35" t="n">
         <v>3.6</v>
       </c>
-      <c r="R35" t="n">
+      <c r="Y35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.35</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.71</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,77 +5055,77 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.49</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="N36" t="n">
-        <v>2.69</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U36" t="n">
         <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.25</v>
       </c>
-      <c r="X36" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.63</v>
+        <v>3.62</v>
       </c>
       <c r="M37" t="n">
-        <v>4.05</v>
+        <v>3.52</v>
       </c>
       <c r="N37" t="n">
-        <v>5.15</v>
+        <v>1.96</v>
       </c>
       <c r="O37" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.8</v>
+        <v>2.53</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>3.9</v>
+        <v>3.83</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.18</v>
+        <v>1.96</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>3.99</v>
       </c>
       <c r="N38" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O38" t="n">
         <v>4.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA38" t="n">
         <v>2.35</v>
       </c>
-      <c r="U38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AB38" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.83</v>
+        <v>4.8</v>
       </c>
       <c r="M39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S39" t="n">
         <v>3.7</v>
       </c>
-      <c r="N39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T39" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U39" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X39" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC39" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="R40" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S40" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U40" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X40" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.91</v>
+        <v>2.71</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.9</v>
+        <v>1.26</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.75</v>
+        <v>2.49</v>
       </c>
       <c r="M41" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="N41" t="n">
-        <v>1.64</v>
+        <v>2.69</v>
       </c>
       <c r="O41" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P41" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="T41" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U41" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>3.38</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>2.99</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N42" t="n">
-        <v>5.75</v>
+        <v>2.17</v>
       </c>
       <c r="O42" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="R42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>2.25</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,58 +5958,58 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>3.21</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.21</v>
+        <v>4.75</v>
       </c>
       <c r="O43" t="n">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="P43" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S43" t="n">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="T43" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U43" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V43" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="X43" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AD43" t="n">
         <v>1.95</v>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.49</v>
+        <v>2.01</v>
       </c>
       <c r="M44" t="n">
-        <v>4.18</v>
+        <v>3.21</v>
       </c>
       <c r="N44" t="n">
-        <v>1.74</v>
+        <v>3.21</v>
       </c>
       <c r="O44" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.15</v>
+        <v>4.15</v>
       </c>
       <c r="R44" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="S44" t="n">
-        <v>3.45</v>
+        <v>2.81</v>
       </c>
       <c r="T44" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="U44" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X44" t="n">
-        <v>4.33</v>
+        <v>3.24</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.48</v>
+        <v>3.18</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
         <v>4.6</v>
@@ -948,13 +948,13 @@
         <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
         <v>2.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
@@ -963,13 +963,13 @@
         <v>1.34</v>
       </c>
       <c r="X4" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AA4" t="n">
         <v>3.72</v>
@@ -978,7 +978,7 @@
         <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD4" t="n">
         <v>1.72</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.29</v>
+        <v>1.94</v>
       </c>
       <c r="AI4" t="n">
         <v>1.6</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.56</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="T5" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AA5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH5" t="n">
         <v>2.41</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AI5" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45951.5</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.41</v>
+        <v>2.06</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45951.5</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="P7" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
         <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB7" t="n">
         <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45951.54166666666</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45951.54166666666</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.48</v>
+        <v>4.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>2.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
         <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>4.32</v>
+        <v>2.68</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.91</v>
+        <v>4.56</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U17" t="n">
         <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>2.68</v>
+        <v>3.64</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.56</v>
+        <v>2.97</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>3.04</v>
       </c>
       <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.23</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X21" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.16</v>
+        <v>1.51</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.84</v>
+        <v>5.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5</v>
+        <v>3.52</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="X22" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.42</v>
+        <v>2.28</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.23</v>
+        <v>1.59</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.51</v>
+        <v>2.16</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,22 +3378,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
-        <v>2.61</v>
+        <v>2.84</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="R23" t="n">
         <v>1.27</v>
@@ -3402,37 +3402,37 @@
         <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X23" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="O24" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>4.33</v>
+        <v>5.09</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="T25" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
         <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>5.09</v>
+        <v>5.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.03</v>
+        <v>2.61</v>
       </c>
       <c r="M26" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="X26" t="n">
-        <v>3.95</v>
+        <v>2.89</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AH26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45951.65625</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="N27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O27" t="n">
         <v>3.4</v>
       </c>
-      <c r="O27" t="n">
-        <v>2.55</v>
-      </c>
       <c r="P27" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
         <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X27" t="n">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45951.65625</v>
@@ -4023,22 +4023,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.78</v>
+        <v>4.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="O28" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R28" t="n">
         <v>1.32</v>
@@ -4053,25 +4053,25 @@
         <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
         <v>3.85</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AC28" t="n">
         <v>1.63</v>
@@ -4096,10 +4096,10 @@
         <v>1.22</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45951.65625</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>2.46</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="N29" t="n">
-        <v>7.2</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
-        <v>2.1</v>
+        <v>3.04</v>
       </c>
       <c r="P29" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.93</v>
+        <v>3.45</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="U29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.37</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.32</v>
       </c>
-      <c r="X29" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH29" t="n">
-        <v>2.24</v>
+        <v>1.54</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45951.65625</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="M31" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="N31" t="n">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="O31" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>2.72</v>
+        <v>3.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA31" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="N32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O32" t="n">
         <v>2.88</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3.1</v>
       </c>
       <c r="P32" t="n">
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.48</v>
+        <v>4.18</v>
       </c>
       <c r="R32" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W32" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X32" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,13 +4609,13 @@
         <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45951.65625</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.41</v>
+        <v>1.62</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>3.97</v>
       </c>
       <c r="N33" t="n">
-        <v>2.82</v>
+        <v>5.45</v>
       </c>
       <c r="O33" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.45</v>
+        <v>5.93</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.62</v>
+        <v>3.24</v>
       </c>
       <c r="AB33" t="n">
         <v>1.26</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.49</v>
+        <v>2.22</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45951.65625</v>
@@ -4797,19 +4797,19 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="M34" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="P34" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q34" t="n">
         <v>3</v>
@@ -4821,7 +4821,7 @@
         <v>2.44</v>
       </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="U34" t="n">
         <v>1.31</v>
@@ -4836,22 +4836,22 @@
         <v>2.68</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AA34" t="n">
         <v>4.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4867,13 +4867,13 @@
         <v>1.34</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45951.65625</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="T35" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V35" t="n">
         <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X35" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AA35" t="n">
         <v>3.35</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>4.1</v>
       </c>
       <c r="M36" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>5.5</v>
+        <v>1.73</v>
       </c>
       <c r="O36" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.8</v>
+        <v>2.18</v>
       </c>
       <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.4</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC36" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,43 +5313,43 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="M38" t="n">
-        <v>3.99</v>
+        <v>3.64</v>
       </c>
       <c r="N38" t="n">
-        <v>1.71</v>
+        <v>2.17</v>
       </c>
       <c r="O38" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P38" t="n">
         <v>2.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="R38" t="n">
         <v>1.29</v>
       </c>
       <c r="S38" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T38" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U38" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X38" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="Y38" t="n">
         <v>1.68</v>
@@ -5358,16 +5358,16 @@
         <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.8</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>1.61</v>
+        <v>2.64</v>
       </c>
       <c r="O39" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="T39" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="X39" t="n">
-        <v>4.55</v>
+        <v>3.38</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,43 +5571,43 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="N40" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O40" t="n">
         <v>4.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S40" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="Y40" t="n">
         <v>1.68</v>
@@ -5616,16 +5616,16 @@
         <v>2.18</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.49</v>
+        <v>1.57</v>
       </c>
       <c r="M41" t="n">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="N41" t="n">
-        <v>2.69</v>
+        <v>5.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T41" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U41" t="n">
         <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
         <v>1.28</v>
       </c>
       <c r="X41" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.99</v>
+        <v>2.01</v>
       </c>
       <c r="M42" t="n">
-        <v>3.64</v>
+        <v>3.21</v>
       </c>
       <c r="N42" t="n">
-        <v>2.17</v>
+        <v>3.21</v>
       </c>
       <c r="O42" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.6</v>
+        <v>4.15</v>
       </c>
       <c r="R42" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S42" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="T42" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="U42" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="X42" t="n">
-        <v>4.25</v>
+        <v>3.24</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.51</v>
+        <v>3.18</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U43" t="n">
         <v>1.62</v>
       </c>
-      <c r="M43" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.5</v>
-      </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X43" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="M44" t="n">
-        <v>3.21</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.21</v>
+        <v>4.75</v>
       </c>
       <c r="O44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T44" t="n">
         <v>2.5</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U44" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W44" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="X44" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AD44" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.77</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.4</v>
+        <v>11.15</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="T2" t="n">
-        <v>3.95</v>
+        <v>2.82</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="X2" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.89</v>
+        <v>1.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.34</v>
+        <v>1.81</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.75</v>
+        <v>3.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,13 +739,13 @@
         <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.79</v>
+        <v>3.42</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45951.45833333334</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>2.57</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.61</v>
+        <v>6.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.91</v>
+        <v>3.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
-        <v>3.22</v>
+        <v>2.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.14</v>
+        <v>5.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.15</v>
+        <v>1.82</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45951.45833333334</v>
@@ -927,58 +927,58 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>5.44</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="T4" t="n">
         <v>2.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AB4" t="n">
         <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AD4" t="n">
         <v>1.72</v>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
         <v>1.94</v>
@@ -1065,7 +1065,7 @@
         <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
         <v>2.5</v>
@@ -1080,7 +1080,7 @@
         <v>3.54</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
         <v>1.63</v>
@@ -1110,7 +1110,7 @@
         <v>1.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="AI5" t="n">
         <v>1.41</v>
@@ -1212,7 +1212,7 @@
         <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
         <v>1.03</v>
@@ -1236,7 +1236,7 @@
         <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AD6" t="n">
         <v>2.08</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>5.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>6.06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="U7" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
         <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.3</v>
+        <v>3.12</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45951.54166666666</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.44</v>
       </c>
-      <c r="M8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.51</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
-        <v>4.45</v>
+        <v>3.74</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.72</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.54</v>
-      </c>
       <c r="AI8" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.12</v>
+        <v>2.3</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45951.54166666666</v>
@@ -1587,7 +1587,7 @@
         <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
         <v>1.2</v>
@@ -1608,7 +1608,7 @@
         <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="Y9" t="n">
         <v>1.37</v>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45951.57291666666</v>
@@ -1710,7 +1710,7 @@
         <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
@@ -1731,7 +1731,7 @@
         <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
         <v>1.36</v>
@@ -1774,10 +1774,10 @@
         <v>1.44</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45951.57291666666</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.48</v>
+        <v>3.63</v>
       </c>
       <c r="P13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,65 +2213,65 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="O15" t="n">
-        <v>4.32</v>
+        <v>4.43</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
         <v>2.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="X15" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.86</v>
+        <v>4.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>4.47</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="X16" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.35</v>
+        <v>3.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
         <v>2.68</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.56</v>
+        <v>4.42</v>
       </c>
       <c r="R17" t="n">
         <v>1.44</v>
@@ -2634,25 +2634,25 @@
         <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.94</v>
+        <v>4.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
         <v>1.91</v>
@@ -2674,13 +2674,13 @@
         <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="T18" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X18" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.27</v>
       </c>
-      <c r="AH18" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>5.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="O19" t="n">
-        <v>3.64</v>
+        <v>6.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.97</v>
+        <v>2.33</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="X19" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45951.60416666666</v>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,31 +3120,31 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="M21" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.04</v>
+        <v>2.47</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="U21" t="n">
         <v>1.33</v>
@@ -3159,22 +3159,22 @@
         <v>2.88</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45951.625</v>
+        <v>45951.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>2.38</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>2.84</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.01</v>
+        <v>3.14</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
         <v>1.6</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.16</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>2.84</v>
+        <v>3.02</v>
       </c>
       <c r="P23" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>2.52</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>3.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="X23" t="n">
-        <v>4.33</v>
+        <v>2.92</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>1.69</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.53</v>
+        <v>3.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.42</v>
+        <v>1.9</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45951.625</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.91</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P24" t="n">
         <v>2.5</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>5.01</v>
       </c>
       <c r="R24" t="n">
         <v>1.23</v>
@@ -3531,37 +3531,37 @@
         <v>3.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.59</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X24" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AD24" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="O25" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U25" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
         <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O26" t="n">
         <v>2.61</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.1</v>
-      </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="T26" t="n">
-        <v>2.95</v>
+        <v>2.18</v>
       </c>
       <c r="U26" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>2.89</v>
+        <v>5.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.13</v>
+        <v>1.62</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>2.23</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.7</v>
+        <v>2.38</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,19 +3832,19 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AI26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45951.65625</v>
+        <v>45951.625</v>
       </c>
     </row>
     <row r="27">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>2.3</v>
+        <v>3.06</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="P27" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>3.61</v>
+        <v>3.85</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
         <v>1.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45951.65625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.25</v>
+        <v>3.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="O28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.34</v>
+        <v>2.79</v>
       </c>
       <c r="R28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.32</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.48</v>
-      </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.18</v>
       </c>
-      <c r="X28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45951.65625</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,19 +4152,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="O29" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q29" t="n">
         <v>3.45</v>
@@ -4173,34 +4173,34 @@
         <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="T29" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AA29" t="n">
         <v>3.62</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AC29" t="n">
         <v>1.82</v>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45951.65625</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.55</v>
+        <v>2.39</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
-        <v>3.9</v>
+        <v>3.06</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.68</v>
+        <v>3.74</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X30" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.42</v>
+        <v>3.62</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45951.65625</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y31" t="n">
         <v>2.03</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Z31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45951.65625</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="M32" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>2.28</v>
       </c>
       <c r="O32" t="n">
-        <v>2.88</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.18</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="T32" t="n">
-        <v>3.22</v>
+        <v>2.81</v>
       </c>
       <c r="U32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.3</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45951.65625</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.62</v>
+        <v>2.86</v>
       </c>
       <c r="M33" t="n">
-        <v>3.97</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>5.45</v>
+        <v>2.46</v>
       </c>
       <c r="O33" t="n">
-        <v>2.1</v>
+        <v>3.79</v>
       </c>
       <c r="P33" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.93</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S33" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="X33" t="n">
-        <v>3.12</v>
+        <v>2.68</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.24</v>
+        <v>4.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.22</v>
+        <v>1.38</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.51</v>
+        <v>2.2</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3.12</v>
+        <v>1.9</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45951.65625</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="M34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O34" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.1</v>
       </c>
-      <c r="N34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.44</v>
-      </c>
       <c r="T34" t="n">
-        <v>3.33</v>
+        <v>2.47</v>
       </c>
       <c r="U34" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>2.68</v>
+        <v>3.85</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.27</v>
+        <v>1.71</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.4</v>
+        <v>2.61</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45951.65625</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,62 +4926,62 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.95</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.75</v>
-      </c>
       <c r="Z35" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AC35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD35" t="n">
         <v>1.78</v>
       </c>
-      <c r="AD35" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45951.65625</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,86 +5055,86 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q36" t="n">
         <v>4.1</v>
       </c>
-      <c r="M36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.18</v>
-      </c>
       <c r="R36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.33</v>
       </c>
-      <c r="S36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45951.66666666666</v>
+        <v>45951.65625</v>
       </c>
     </row>
     <row r="37">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.62</v>
+        <v>1.62</v>
       </c>
       <c r="M37" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>1.96</v>
+        <v>4.75</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="P37" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.53</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X37" t="n">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.96</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.99</v>
+        <v>3.62</v>
       </c>
       <c r="M38" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="N38" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="O38" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="R38" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T38" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="U38" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W38" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X38" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5383,13 +5383,13 @@
         <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.64</v>
       </c>
       <c r="N39" t="n">
-        <v>2.64</v>
+        <v>2.17</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="P39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD39" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q39" t="n">
-        <v>3</v>
-      </c>
-      <c r="R39" t="n">
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.36</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="Y39" t="n">
+      <c r="AI39" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>2</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5622,10 +5622,10 @@
         <v>1.52</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5644,10 +5644,10 @@
         <v>1.16</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5718,7 +5718,7 @@
         <v>4.8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
         <v>2.9</v>
@@ -5733,10 +5733,10 @@
         <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X41" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="Y41" t="n">
         <v>1.89</v>
@@ -5745,16 +5745,16 @@
         <v>1.85</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="AB41" t="n">
         <v>1.3</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5773,10 +5773,10 @@
         <v>2.3</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3.21</v>
+        <v>4.2</v>
       </c>
       <c r="N42" t="n">
-        <v>3.21</v>
+        <v>1.61</v>
       </c>
       <c r="O42" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.09</v>
+        <v>2.65</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.15</v>
+        <v>2.13</v>
       </c>
       <c r="R42" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>2.81</v>
+        <v>3.6</v>
       </c>
       <c r="T42" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="U42" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X42" t="n">
-        <v>3.24</v>
+        <v>4.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.76</v>
+        <v>2.43</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.18</v>
+        <v>2.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD42" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.64</v>
+        <v>1.18</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="N43" t="n">
-        <v>1.61</v>
+        <v>2.62</v>
       </c>
       <c r="O43" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P43" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.13</v>
+        <v>3.06</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>3.7</v>
+        <v>3.09</v>
       </c>
       <c r="T43" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="U43" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X43" t="n">
-        <v>4.55</v>
+        <v>3.38</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.43</v>
+        <v>1.89</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45951.66666666666</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,43 +6087,43 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.62</v>
+        <v>4.1</v>
       </c>
       <c r="M44" t="n">
         <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>4.75</v>
+        <v>1.73</v>
       </c>
       <c r="O44" t="n">
-        <v>2.05</v>
+        <v>4.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="R44" t="n">
         <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U44" t="n">
         <v>1.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X44" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Y44" t="n">
         <v>1.68</v>
@@ -6132,16 +6132,16 @@
         <v>2.18</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB44" t="n">
         <v>1.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,16 +6154,16 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45951.66666666666</v>
@@ -6175,126 +6175,255 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Northampton Town</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>45951.66666666666</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Luxembourg National Division</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Swift Hesperange</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Racing</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" s="3" t="n">
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3" t="n">
         <v>45951.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK46"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.72</v>
+        <v>2.57</v>
       </c>
       <c r="P2" t="n">
-        <v>2.52</v>
+        <v>1.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.15</v>
+        <v>6.01</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.82</v>
+        <v>3.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>3.22</v>
+        <v>2.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.81</v>
+        <v>1.37</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.14</v>
+        <v>5.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.42</v>
+        <v>1.82</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45951.45833333334</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>2.57</v>
+        <v>1.72</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>2.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.01</v>
+        <v>11.15</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="T3" t="n">
-        <v>3.94</v>
+        <v>2.82</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.75</v>
+        <v>3.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.82</v>
+        <v>3.42</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45951.45833333334</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="U5" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AI5" t="n">
         <v>1.41</v>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="Q6" t="n">
         <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V6" t="n">
         <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
         <v>1.59</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AI6" t="n">
         <v>1.57</v>
@@ -1572,31 +1572,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
         <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>1.75</v>
@@ -1605,44 +1605,44 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.11</v>
       </c>
-      <c r="X9" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AI9" t="n">
         <v>1.25</v>
@@ -1701,31 +1701,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="O10" t="n">
         <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
         <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
         <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="U10" t="n">
         <v>1.33</v>
@@ -1740,13 +1740,13 @@
         <v>2.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AB10" t="n">
         <v>1.22</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45951.58333333334</v>
+        <v>45951.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="O13" t="n">
-        <v>3.63</v>
+        <v>4.43</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="T13" t="n">
-        <v>3.06</v>
+        <v>3.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>1.33</v>
       </c>
-      <c r="X13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AH13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,65 +2213,65 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.45</v>
+        <v>5.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="N15" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
-        <v>4.43</v>
+        <v>6.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.91</v>
+        <v>2.33</v>
       </c>
       <c r="R15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.52</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.46</v>
-      </c>
       <c r="X15" t="n">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AB15" t="n">
         <v>1.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,52 +2475,52 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.65</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
-        <v>4.47</v>
+        <v>2.47</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.56</v>
+        <v>3.86</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
         <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.79</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
         <v>1.22</v>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="AI16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.72</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,65 +2858,65 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.47</v>
+        <v>2.84</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.86</v>
+        <v>3.14</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>2.96</v>
+        <v>2.34</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
         <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>2.88</v>
+        <v>4.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.68</v>
+        <v>2.27</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.86</v>
+        <v>2.42</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45951.60416666666</v>
+        <v>45951.625</v>
       </c>
     </row>
     <row r="22">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2.84</v>
+        <v>3.02</v>
       </c>
       <c r="P22" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>3.35</v>
+        <v>2.52</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4</v>
+        <v>3.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="X22" t="n">
-        <v>4.33</v>
+        <v>2.92</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.35</v>
+        <v>1.69</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.53</v>
+        <v>3.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.42</v>
+        <v>1.9</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45951.625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
-        <v>3.02</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.84</v>
+        <v>4.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>2.52</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>3.11</v>
+        <v>2.21</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>2.92</v>
+        <v>5.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.69</v>
+        <v>2.62</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.51</v>
+        <v>2.21</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45951.625</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.01</v>
+        <v>3.76</v>
       </c>
       <c r="R24" t="n">
         <v>1.23</v>
@@ -3531,37 +3531,37 @@
         <v>3.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V24" t="n">
         <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.46</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD24" t="n">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45951.625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="R25" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="T25" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
-        <v>5.09</v>
+        <v>4.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45951.625</v>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
-        <v>2.61</v>
+        <v>3.06</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.02</v>
+        <v>3.74</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>3.35</v>
+        <v>2.59</v>
       </c>
       <c r="T26" t="n">
-        <v>2.18</v>
+        <v>3.21</v>
       </c>
       <c r="U26" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="X26" t="n">
-        <v>5.2</v>
+        <v>2.89</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.38</v>
+        <v>3.62</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.39</v>
+        <v>1.88</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,19 +3832,19 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
         <v>1.54</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45951.625</v>
+        <v>45951.65625</v>
       </c>
     </row>
     <row r="27">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.03</v>
+        <v>3.28</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>3.06</v>
+        <v>2.08</v>
       </c>
       <c r="O27" t="n">
-        <v>2.63</v>
+        <v>4.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>2.79</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="T27" t="n">
-        <v>2.6</v>
+        <v>3.29</v>
       </c>
       <c r="U27" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.18</v>
       </c>
-      <c r="X27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y27" t="n">
+      <c r="AC27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>2.35</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45951.65625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
         <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>2.08</v>
+        <v>2.76</v>
       </c>
       <c r="O28" t="n">
-        <v>4.1</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.79</v>
+        <v>3.45</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="T28" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
         <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
         <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.88</v>
+        <v>3.62</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45951.65625</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.89</v>
       </c>
       <c r="N29" t="n">
-        <v>2.76</v>
+        <v>5.63</v>
       </c>
       <c r="O29" t="n">
-        <v>3.22</v>
+        <v>2.16</v>
       </c>
       <c r="P29" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.45</v>
+        <v>5.93</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="U29" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="X29" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.62</v>
+        <v>3.18</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.47</v>
+        <v>2.24</v>
       </c>
       <c r="AI29" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.1</v>
+        <v>3.12</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45951.65625</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q30" t="n">
         <v>2.9</v>
       </c>
-      <c r="O30" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.74</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="T30" t="n">
-        <v>3.21</v>
+        <v>2.81</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>2.89</v>
+        <v>3.61</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="Z30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA30" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45951.65625</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="M31" t="n">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="O31" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="T31" t="n">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X31" t="n">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.03</v>
+        <v>2.31</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="AB31" t="n">
         <v>1.22</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45951.65625</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.73</v>
+        <v>2.08</v>
       </c>
       <c r="M32" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.28</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>3.78</v>
+        <v>2.57</v>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>3.94</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>3.61</v>
+        <v>3.86</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.29</v>
+        <v>2.74</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45951.65625</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.86</v>
+        <v>2.09</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="N33" t="n">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
-        <v>3.79</v>
+        <v>2.7</v>
       </c>
       <c r="P33" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>4.13</v>
       </c>
       <c r="R33" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="T33" t="n">
-        <v>3.28</v>
+        <v>2.96</v>
       </c>
       <c r="U33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.29</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45951.65625</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.62</v>
+        <v>2.86</v>
       </c>
       <c r="M35" t="n">
-        <v>3.89</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>5.63</v>
+        <v>2.46</v>
       </c>
       <c r="O35" t="n">
-        <v>2.16</v>
+        <v>3.79</v>
       </c>
       <c r="P35" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.93</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="S35" t="n">
-        <v>2.77</v>
+        <v>2.44</v>
       </c>
       <c r="T35" t="n">
-        <v>2.81</v>
+        <v>3.28</v>
       </c>
       <c r="U35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.38</v>
       </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AI35" t="n">
-        <v>1.51</v>
+        <v>2.2</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.12</v>
+        <v>1.9</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45951.65625</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,62 +5055,62 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="M36" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="O36" t="n">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="P36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD36" t="n">
         <v>1.97</v>
       </c>
-      <c r="Q36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5122,19 +5122,19 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45951.65625</v>
+        <v>45951.66666666666</v>
       </c>
     </row>
     <row r="37">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.62</v>
+        <v>4.87</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>4.28</v>
       </c>
       <c r="N37" t="n">
-        <v>4.75</v>
+        <v>1.67</v>
       </c>
       <c r="O37" t="n">
-        <v>2.05</v>
+        <v>4.4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S37" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X37" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5254,13 +5254,13 @@
         <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.62</v>
+        <v>1.44</v>
       </c>
       <c r="M38" t="n">
-        <v>3.52</v>
+        <v>4.05</v>
       </c>
       <c r="N38" t="n">
-        <v>1.96</v>
+        <v>5.3</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="P38" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.53</v>
+        <v>4.8</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="U38" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X38" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC38" t="n">
         <v>1.73</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.99</v>
+        <v>2.54</v>
       </c>
       <c r="M39" t="n">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="N39" t="n">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="O39" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.6</v>
+        <v>3.06</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="T39" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="U39" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V39" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="X39" t="n">
-        <v>4.33</v>
+        <v>3.38</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="M40" t="n">
-        <v>3.99</v>
+        <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="O40" t="n">
         <v>4.5</v>
@@ -5586,7 +5586,7 @@
         <v>2.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="R40" t="n">
         <v>1.29</v>
@@ -5595,7 +5595,7 @@
         <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="U40" t="n">
         <v>1.57</v>
@@ -5610,19 +5610,19 @@
         <v>4.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD40" t="n">
         <v>2.25</v>
@@ -5641,7 +5641,7 @@
         <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI40" t="n">
         <v>2.4</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.57</v>
+        <v>4.82</v>
       </c>
       <c r="M41" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="N41" t="n">
-        <v>5.5</v>
+        <v>1.66</v>
       </c>
       <c r="O41" t="n">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="U41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.4</v>
       </c>
-      <c r="V41" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC41" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5770,13 +5770,13 @@
         <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.87</v>
+        <v>1.53</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.8</v>
+        <v>3.86</v>
       </c>
       <c r="M42" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="N42" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="O42" t="n">
         <v>4.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="R42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W42" t="n">
         <v>1.25</v>
       </c>
-      <c r="S42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.17</v>
-      </c>
       <c r="X42" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.54</v>
+        <v>1.61</v>
       </c>
       <c r="M43" t="n">
-        <v>3.38</v>
+        <v>3.95</v>
       </c>
       <c r="N43" t="n">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="O43" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P43" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.06</v>
+        <v>5.5</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="T43" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U43" t="n">
         <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W43" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X43" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AI43" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45951.66666666666</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="O44" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S44" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T44" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U44" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V44" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W44" t="n">
         <v>1.2</v>
       </c>
       <c r="X44" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,16 +6154,16 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45951.66666666666</v>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,147 +6283,18 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45951.66666666666</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45951</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Luxembourg National Division</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Swift Hesperange</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Racing</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" s="3" t="n">
         <v>45951.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,58 +669,58 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>2.57</v>
+        <v>1.75</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.01</v>
+        <v>8.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
-        <v>3.94</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.75</v>
+        <v>3.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="AD2" t="n">
         <v>1.48</v>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.82</v>
+        <v>3.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45951.45833333334</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.72</v>
+        <v>2.57</v>
       </c>
       <c r="P3" t="n">
-        <v>2.52</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.15</v>
+        <v>6.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="S3" t="n">
-        <v>2.66</v>
+        <v>2.17</v>
       </c>
       <c r="T3" t="n">
-        <v>2.82</v>
+        <v>3.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="X3" t="n">
-        <v>3.22</v>
+        <v>2.15</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.81</v>
+        <v>1.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.14</v>
+        <v>5.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.42</v>
+        <v>1.85</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45951.45833333334</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.44</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AB4" t="n">
         <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AI4" t="n">
         <v>1.6</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.57</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45951.5</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.56</v>
+        <v>4.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="T6" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="U6" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>4.15</v>
+        <v>4.65</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45951.5</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.44</v>
       </c>
-      <c r="M7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.46</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>3.12</v>
+        <v>2.3</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45951.54166666666</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>3.58</v>
+        <v>5.75</v>
       </c>
       <c r="O8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.52</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.76</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AD8" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.3</v>
+        <v>3.12</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45951.54166666666</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.19</v>
+        <v>2.76</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>3.21</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>2.67</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X9" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6.5</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.91</v>
+        <v>4.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
         <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45951.57291666666</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.76</v>
+        <v>1.19</v>
       </c>
       <c r="M10" t="n">
-        <v>3.21</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.67</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>3.24</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.33</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.05</v>
+        <v>1.91</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45951.57291666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>4.47</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.79</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="O14" t="n">
-        <v>3.63</v>
+        <v>3.15</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AI14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.15</v>
+        <v>3.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>6.25</v>
+        <v>4.49</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="R15" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="X15" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AB15" t="n">
         <v>1.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.26</v>
       </c>
-      <c r="AH15" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,22 +2475,22 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.98</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.97</v>
-      </c>
       <c r="Q16" t="n">
-        <v>3.86</v>
+        <v>4.47</v>
       </c>
       <c r="R16" t="n">
         <v>1.44</v>
@@ -2499,37 +2499,37 @@
         <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>3.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.68</v>
+        <v>3.74</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.42</v>
+        <v>2.59</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="X17" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.31</v>
+        <v>3.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.72</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2736,7 +2736,7 @@
         <v>3.35</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
         <v>2.15</v>
@@ -2763,22 +2763,22 @@
         <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X18" t="n">
         <v>2.74</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.88</v>
+        <v>4.01</v>
       </c>
       <c r="AB18" t="n">
         <v>1.18</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,65 +2858,65 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45951.60416666666</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>4.51</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>3.24</v>
+        <v>2.96</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="X20" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45951.60416666666</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="M21" t="n">
         <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="P21" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.14</v>
+        <v>3.37</v>
       </c>
       <c r="R21" t="n">
         <v>1.27</v>
@@ -3144,10 +3144,10 @@
         <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
         <v>1.03</v>
@@ -3156,25 +3156,25 @@
         <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,13 +3190,13 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45951.625</v>
@@ -3252,74 +3252,74 @@
         <v>2.25</v>
       </c>
       <c r="M22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O22" t="n">
         <v>3.1</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.02</v>
-      </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="T22" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="U22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.33</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AI22" t="n">
         <v>1.95</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.84</v>
+        <v>3.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="T23" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.21</v>
+        <v>1.76</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45951.625</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="M24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S24" t="n">
         <v>3.6</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.52</v>
-      </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="U24" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.52</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AD24" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.76</v>
+        <v>2.21</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45951.625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,22 +3636,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
         <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.37</v>
+        <v>3.14</v>
       </c>
       <c r="R25" t="n">
         <v>1.27</v>
@@ -3660,10 +3660,10 @@
         <v>3.35</v>
       </c>
       <c r="T25" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U25" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
@@ -3672,25 +3672,25 @@
         <v>1.14</v>
       </c>
       <c r="X25" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3706,13 +3706,13 @@
         <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45951.625</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="O26" t="n">
-        <v>3.06</v>
+        <v>3.41</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="X26" t="n">
-        <v>2.89</v>
+        <v>3.38</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.62</v>
+        <v>3.12</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45951.65625</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.28</v>
+        <v>2.41</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>2.08</v>
+        <v>2.82</v>
       </c>
       <c r="O27" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.79</v>
+        <v>3.29</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S27" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="T27" t="n">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X27" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45951.65625</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>2.76</v>
+        <v>7.2</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>2.16</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.45</v>
+        <v>5.93</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
         <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.62</v>
+        <v>3.18</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.47</v>
+        <v>2.24</v>
       </c>
       <c r="AI28" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.1</v>
+        <v>3.12</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45951.65625</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="M29" t="n">
-        <v>3.89</v>
+        <v>3.58</v>
       </c>
       <c r="N29" t="n">
-        <v>5.63</v>
+        <v>1.9</v>
       </c>
       <c r="O29" t="n">
-        <v>2.16</v>
+        <v>3.86</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.93</v>
+        <v>2.34</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>3.18</v>
+        <v>3.85</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.12</v>
+        <v>1.57</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45951.65625</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="N30" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>3.78</v>
+        <v>3.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.81</v>
+        <v>2.58</v>
       </c>
       <c r="T30" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="X30" t="n">
-        <v>3.61</v>
+        <v>2.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AI30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45951.65625</v>
@@ -4410,19 +4410,19 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="M31" t="n">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="O31" t="n">
-        <v>2.91</v>
+        <v>2.68</v>
       </c>
       <c r="P31" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
         <v>4.1</v>
@@ -4431,7 +4431,7 @@
         <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
         <v>3.22</v>
@@ -4440,25 +4440,25 @@
         <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
         <v>1.36</v>
       </c>
       <c r="X31" t="n">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.92</v>
+        <v>4.32</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC31" t="n">
         <v>1.91</v>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
         <v>1.6</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.08</v>
+        <v>3.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>2.57</v>
+        <v>4.06</v>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>1.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.94</v>
+        <v>2.85</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
-        <v>2.6</v>
+        <v>3.18</v>
       </c>
       <c r="U32" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="X32" t="n">
-        <v>3.86</v>
+        <v>2.81</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.74</v>
+        <v>3.98</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45951.65625</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M33" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="O33" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="P33" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.13</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S33" t="n">
-        <v>2.59</v>
+        <v>3.14</v>
       </c>
       <c r="T33" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.84</v>
+        <v>3</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45951.65625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>4.52</v>
+        <v>2.7</v>
       </c>
       <c r="P34" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.34</v>
+        <v>4.26</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X34" t="n">
         <v>3.1</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.85</v>
-      </c>
       <c r="Y34" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.61</v>
+        <v>3.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45951.65625</v>
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.86</v>
+        <v>3.09</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="N35" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="O35" t="n">
         <v>3.79</v>
@@ -4956,7 +4956,7 @@
         <v>1.29</v>
       </c>
       <c r="V35" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W35" t="n">
         <v>1.4</v>
@@ -4965,10 +4965,10 @@
         <v>2.68</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AA35" t="n">
         <v>4.5</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N36" t="n">
-        <v>3.75</v>
+        <v>2.69</v>
       </c>
       <c r="O36" t="n">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="P36" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.2</v>
+        <v>3.06</v>
       </c>
       <c r="R36" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="T36" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U36" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X36" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.87</v>
+        <v>2.01</v>
       </c>
       <c r="M37" t="n">
-        <v>4.28</v>
+        <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>1.67</v>
+        <v>3.21</v>
       </c>
       <c r="O37" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="P37" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.15</v>
+        <v>4.32</v>
       </c>
       <c r="R37" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S37" t="n">
-        <v>3.6</v>
+        <v>2.77</v>
       </c>
       <c r="T37" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="U37" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="X37" t="n">
-        <v>4.8</v>
+        <v>3.24</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.37</v>
+        <v>1.76</v>
       </c>
       <c r="AA37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.5</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="M38" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="N38" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="R38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.3</v>
       </c>
-      <c r="S38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC38" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
         <v>2.3</v>
@@ -5389,7 +5389,7 @@
         <v>1.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.54</v>
+        <v>3.14</v>
       </c>
       <c r="M39" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P39" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.06</v>
+        <v>2.63</v>
       </c>
       <c r="R39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.36</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AI39" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.82</v>
+        <v>4.87</v>
       </c>
       <c r="M41" t="n">
-        <v>3.75</v>
+        <v>4.28</v>
       </c>
       <c r="N41" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O41" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T41" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V41" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.22</v>
       </c>
-      <c r="X41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" t="n">
         <v>2.6</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.86</v>
+        <v>4.82</v>
       </c>
       <c r="M42" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="N42" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="O42" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="U42" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
         <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X42" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AA42" t="n">
         <v>2.88</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45951.66666666666</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.61</v>
+        <v>3.86</v>
       </c>
       <c r="M43" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="N43" t="n">
-        <v>5.1</v>
+        <v>1.91</v>
       </c>
       <c r="O43" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="R43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.36</v>
       </c>
-      <c r="S43" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W43" t="n">
+      <c r="AC43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH43" t="n">
         <v>1.29</v>
       </c>
-      <c r="X43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AI43" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45951.66666666666</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.14</v>
+        <v>1.44</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N44" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="O44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S44" t="n">
         <v>3.3</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T44" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="U44" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
         <v>1.2</v>
       </c>
       <c r="X44" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Y44" t="n">
         <v>1.67</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH44" t="n">
         <v>2.3</v>
       </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI44" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45951.66666666666</v>

--- a/jogos_2025-10-21.xlsx
+++ b/jogos_2025-10-21.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,58 +669,58 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="M2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N2" t="n">
         <v>4.5</v>
       </c>
-      <c r="N2" t="n">
-        <v>10</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.5</v>
+        <v>5.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.85</v>
+        <v>2.17</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7</v>
+        <v>3.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>2.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.3</v>
+        <v>5.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="AD2" t="n">
         <v>1.48</v>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.15</v>
+        <v>1.87</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45951.45833333334</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,58 +798,58 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>2.57</v>
+        <v>1.75</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.01</v>
+        <v>9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="T3" t="n">
-        <v>3.94</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.89</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.75</v>
+        <v>3.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="AD3" t="n">
         <v>1.48</v>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.85</v>
+        <v>3.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45951.45833333334</v>
@@ -936,22 +936,22 @@
         <v>5.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
         <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
         <v>1.36</v>
@@ -972,16 +972,16 @@
         <v>1.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AB4" t="n">